--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC13" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_South_Kore" displayName="AveragesTable_South_Kore" ref="A1:EC13" headerRowCount="1">
   <autoFilter ref="A1:EC13"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
         <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="G2" t="n">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="H2" t="n">
-        <v>105.22</v>
+        <v>105.47</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>5.32</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="M2" t="n">
-        <v>68.67</v>
+        <v>69.42</v>
       </c>
       <c r="N2" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="O2" t="n">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="P2" t="n">
-        <v>10.28</v>
+        <v>10.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.94</v>
+        <v>11.42</v>
       </c>
       <c r="R2" t="n">
-        <v>7.39</v>
+        <v>7.32</v>
       </c>
       <c r="S2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T2" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>48.78</v>
+        <v>49.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.61</v>
+        <v>13.53</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.720000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="AB2" t="n">
         <v>4.89</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.5</v>
+        <v>17.47</v>
       </c>
       <c r="AD2" t="n">
         <v>1.7</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AF2" t="n">
         <v>0.11</v>
@@ -1550,70 +1550,70 @@
         <v>2.44</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.279999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BO2" t="n">
         <v>1.08</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.97</v>
+        <v>5.08</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.44</v>
+        <v>94.59</v>
       </c>
       <c r="BS2" t="n">
-        <v>75</v>
+        <v>72.97</v>
       </c>
       <c r="BT2" t="n">
-        <v>55.56</v>
+        <v>54.05</v>
       </c>
       <c r="BU2" t="n">
-        <v>22.22</v>
+        <v>21.62</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>61.11</v>
+        <v>59.46</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CA2" t="n">
         <v>3.28</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CC2" t="n">
         <v>3.61</v>
@@ -1625,19 +1625,19 @@
         <v>1.43</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CH2" t="n">
         <v>1.37</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK2" t="n">
         <v>1.71</v>
@@ -1646,19 +1646,19 @@
         <v>2.26</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CO2" t="n">
         <v>1.33</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CR2" t="n">
         <v>1.47</v>
@@ -1673,106 +1673,106 @@
         <v>1.38</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CW2" t="n">
         <v>1.88</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="DE2" t="n">
         <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="DH2" t="n">
-        <v>99.52</v>
+        <v>99.81</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.08</v>
+        <v>4.27</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DM2" t="n">
-        <v>63.56</v>
+        <v>64.08</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.11</v>
+        <v>11.08</v>
       </c>
       <c r="DQ2" t="n">
-        <v>9.609999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.98</v>
+        <v>8.9</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.97</v>
+        <v>46.19</v>
       </c>
       <c r="DW2" t="n">
         <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.66</v>
+        <v>12.65</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.17</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.5</v>
+        <v>4.51</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.84</v>
+        <v>18.3</v>
       </c>
       <c r="EB2" t="n">
         <v>1.58</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="3">
@@ -2185,61 +2185,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
         <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="H4" t="n">
-        <v>119.94</v>
+        <v>119.26</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="K4" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="L4" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="M4" t="n">
-        <v>71.28</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="O4" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>9.94</v>
+        <v>10.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.11</v>
+        <v>11.16</v>
       </c>
       <c r="R4" t="n">
-        <v>6.94</v>
+        <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="U4" t="n">
         <v>0.11</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>53.44</v>
+        <v>52.79</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.89</v>
+        <v>11.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.44</v>
+        <v>7.16</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="AC4" t="n">
-        <v>16.94</v>
+        <v>16</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF4" t="n">
         <v>0.33</v>
@@ -2356,61 +2356,61 @@
         <v>1.78</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.529999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.11</v>
+        <v>3.97</v>
       </c>
       <c r="BR4" t="n">
-        <v>91.67</v>
+        <v>91.89</v>
       </c>
       <c r="BS4" t="n">
-        <v>80.56</v>
+        <v>81.08</v>
       </c>
       <c r="BT4" t="n">
-        <v>55.56</v>
+        <v>54.05</v>
       </c>
       <c r="BU4" t="n">
-        <v>36.11</v>
+        <v>35.14</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.11</v>
+        <v>10.81</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>61.11</v>
+        <v>62.16</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BZ4" t="n">
         <v>2.5</v>
@@ -2446,10 +2446,10 @@
         <v>1.76</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CM4" t="n">
         <v>1.9</v>
@@ -2461,7 +2461,7 @@
         <v>1.28</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ4" t="n">
         <v>3.36</v>
@@ -2470,10 +2470,10 @@
         <v>1.45</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CU4" t="n">
         <v>1.4</v>
@@ -2485,10 +2485,10 @@
         <v>1.8</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CZ4" t="n">
         <v>1.96</v>
@@ -2503,82 +2503,82 @@
         <v>2.01</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="DH4" t="n">
-        <v>107.36</v>
+        <v>107.35</v>
       </c>
       <c r="DI4" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DK4" t="n">
         <v>3.89</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="DM4" t="n">
-        <v>66.22</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.72</v>
+        <v>10.76</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10</v>
+        <v>10.06</v>
       </c>
       <c r="DR4" t="n">
         <v>7.97</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>51</v>
+        <v>50.73</v>
       </c>
       <c r="DW4" t="n">
         <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.48</v>
+        <v>11.33</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.19</v>
+        <v>7.05</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.28</v>
+        <v>16.78</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="5">
@@ -2588,61 +2588,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
         <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="G5" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="H5" t="n">
-        <v>106.22</v>
+        <v>105.37</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K5" t="n">
-        <v>5.94</v>
+        <v>5.79</v>
       </c>
       <c r="L5" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="M5" t="n">
-        <v>69.78</v>
+        <v>68.89</v>
       </c>
       <c r="N5" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="O5" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="P5" t="n">
-        <v>8.779999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.83</v>
+        <v>11.79</v>
       </c>
       <c r="R5" t="n">
-        <v>5.5</v>
+        <v>5.68</v>
       </c>
       <c r="S5" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="T5" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="U5" t="n">
         <v>0.11</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>56.56</v>
+        <v>55.95</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.17</v>
+        <v>17.68</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.28</v>
+        <v>11.84</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.89</v>
+        <v>5.84</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.61</v>
+        <v>18.53</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AF5" t="n">
         <v>0.06</v>
@@ -2759,70 +2759,70 @@
         <v>1.61</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.029999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.83</v>
+        <v>4.76</v>
       </c>
       <c r="BR5" t="n">
-        <v>86.11</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>66.67</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>47.22</v>
+        <v>48.65</v>
       </c>
       <c r="BU5" t="n">
-        <v>33.33</v>
+        <v>35.14</v>
       </c>
       <c r="BV5" t="n">
-        <v>19.44</v>
+        <v>18.92</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="BX5" t="n">
-        <v>61.11</v>
+        <v>62.16</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CA5" t="n">
         <v>3.26</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CC5" t="n">
         <v>2.28</v>
@@ -2834,25 +2834,25 @@
         <v>1.44</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CH5" t="n">
         <v>1.35</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK5" t="n">
         <v>1.76</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CM5" t="n">
         <v>1.99</v>
@@ -2861,127 +2861,127 @@
         <v>1.6</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX5" t="n">
         <v>1.78</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DA5" t="n">
         <v>1.64</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="DH5" t="n">
-        <v>102.39</v>
+        <v>102.06</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.66</v>
+        <v>5.6</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM5" t="n">
-        <v>68.53</v>
+        <v>68.11</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="DP5" t="n">
-        <v>9.779999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.83</v>
+        <v>10.84</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.34</v>
+        <v>6.4</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.5</v>
+        <v>54.24</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.78</v>
+        <v>15.59</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.64</v>
+        <v>10.46</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.94</v>
+        <v>18.41</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="n">
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,43 +3084,43 @@
         <v>0.11</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AI6" t="n">
-        <v>91.89</v>
+        <v>94.16</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.61</v>
+        <v>3.79</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="AN6" t="n">
-        <v>52.28</v>
+        <v>53.42</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.22</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>11.05</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.779999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="AT6" t="n">
         <v>1.11</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>45.61</v>
+        <v>46.32</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.390000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.22</v>
+        <v>6.21</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.78</v>
+        <v>16.79</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="BG6" t="n">
         <v>2.08</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.56</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI6" t="n">
         <v>2.08</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="BO6" t="n">
         <v>0.78</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.53</v>
+        <v>3.41</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.58</v>
+        <v>4.43</v>
       </c>
       <c r="BR6" t="n">
-        <v>83.33</v>
+        <v>83.78</v>
       </c>
       <c r="BS6" t="n">
-        <v>55.56</v>
+        <v>56.76</v>
       </c>
       <c r="BT6" t="n">
-        <v>41.67</v>
+        <v>40.54</v>
       </c>
       <c r="BU6" t="n">
-        <v>19.44</v>
+        <v>18.92</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BX6" t="n">
-        <v>38.89</v>
+        <v>40.54</v>
       </c>
       <c r="BY6" t="n">
         <v>2.65</v>
@@ -3231,13 +3231,13 @@
         <v>3.22</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CE6" t="n">
         <v>1.46</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CG6" t="n">
         <v>2.63</v>
@@ -3246,7 +3246,7 @@
         <v>1.34</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.9</v>
@@ -3255,7 +3255,7 @@
         <v>1.84</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CM6" t="n">
         <v>1.91</v>
@@ -3264,31 +3264,31 @@
         <v>1.55</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CU6" t="n">
         <v>1.36</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX6" t="n">
         <v>1.88</v>
@@ -3306,85 +3306,85 @@
         <v>1.41</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="DE6" t="n">
         <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="DH6" t="n">
-        <v>93.5</v>
+        <v>94.62</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.28</v>
+        <v>4.35</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DM6" t="n">
-        <v>56.28</v>
+        <v>56.76</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.7</v>
+        <v>11.62</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.2</v>
+        <v>11.22</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.31</v>
+        <v>7.16</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.28</v>
+        <v>48.57</v>
       </c>
       <c r="DW6" t="n">
         <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.23</v>
+        <v>10.22</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.44</v>
+        <v>6.43</v>
       </c>
       <c r="DZ6" t="n">
         <v>3.78</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.06</v>
+        <v>18.51</v>
       </c>
       <c r="EB6" t="n">
         <v>1.32</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
         <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="F7" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="G7" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="H7" t="n">
-        <v>114.06</v>
+        <v>112.63</v>
       </c>
       <c r="I7" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="J7" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="K7" t="n">
-        <v>3.83</v>
+        <v>3.63</v>
       </c>
       <c r="L7" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="M7" t="n">
-        <v>79.06</v>
+        <v>77.37</v>
       </c>
       <c r="N7" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="O7" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="P7" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.94</v>
+        <v>14</v>
       </c>
       <c r="R7" t="n">
-        <v>6.89</v>
+        <v>7.11</v>
       </c>
       <c r="S7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="U7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="V7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>50.5</v>
+        <v>50.26</v>
       </c>
       <c r="Y7" t="n">
         <v>0.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.28</v>
+        <v>12</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.390000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.89</v>
+        <v>3.79</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.89</v>
+        <v>15.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AF7" t="n">
         <v>0.06</v>
@@ -3565,64 +3565,64 @@
         <v>2.39</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="BH7" t="n">
         <v>8.109999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO7" t="n">
         <v>0.92</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.72</v>
+        <v>4.57</v>
       </c>
       <c r="BR7" t="n">
-        <v>91.67</v>
+        <v>91.89</v>
       </c>
       <c r="BS7" t="n">
-        <v>58.33</v>
+        <v>59.46</v>
       </c>
       <c r="BT7" t="n">
-        <v>38.89</v>
+        <v>37.84</v>
       </c>
       <c r="BU7" t="n">
-        <v>16.67</v>
+        <v>16.22</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BX7" t="n">
-        <v>44.44</v>
+        <v>43.24</v>
       </c>
       <c r="BY7" t="n">
         <v>2.43</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CA7" t="n">
         <v>3.14</v>
@@ -3649,16 +3649,16 @@
         <v>1.33</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK7" t="n">
         <v>1.84</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CM7" t="n">
         <v>1.89</v>
@@ -3667,13 +3667,13 @@
         <v>1.54</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="CR7" t="n">
         <v>1.53</v>
@@ -3712,82 +3712,82 @@
         <v>2.36</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>105.34</v>
+        <v>104.84</v>
       </c>
       <c r="DI7" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>67.76000000000001</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="DS7" t="n">
         <v>0.16</v>
       </c>
-      <c r="DJ7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>68.33</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>12.42</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>0.17</v>
-      </c>
       <c r="DT7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.72</v>
+        <v>48.64</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.92</v>
+        <v>10.81</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.19</v>
+        <v>7.13</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.2</v>
+        <v>16.7</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="8">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" t="n">
         <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
         <v>0.16</v>
@@ -4293,136 +4293,136 @@
         <v>0.06</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AI9" t="n">
-        <v>96.34999999999999</v>
+        <v>94.83</v>
       </c>
       <c r="AJ9" t="n">
         <v>0.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="AN9" t="n">
-        <v>58.24</v>
+        <v>57.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AP9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>46.83</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BN9" t="n">
         <v>1.35</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>13.35</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>16.35</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1.39</v>
-      </c>
       <c r="BO9" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.44</v>
+        <v>91.89</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.78</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>48.65</v>
       </c>
       <c r="BU9" t="n">
-        <v>27.78</v>
+        <v>27.03</v>
       </c>
       <c r="BV9" t="n">
-        <v>8.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>55.56</v>
+        <v>54.05</v>
       </c>
       <c r="BY9" t="n">
         <v>1.93</v>
@@ -4431,31 +4431,31 @@
         <v>2.03</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="CE9" t="n">
         <v>1.39</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CH9" t="n">
         <v>1.41</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.77</v>
@@ -4464,7 +4464,7 @@
         <v>1.74</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CM9" t="n">
         <v>2.02</v>
@@ -4479,7 +4479,7 @@
         <v>1.95</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CR9" t="n">
         <v>1.44</v>
@@ -4491,7 +4491,7 @@
         <v>2.89</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV9" t="n">
         <v>2.09</v>
@@ -4500,16 +4500,16 @@
         <v>1.82</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CY9" t="n">
         <v>2.2</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DB9" t="n">
         <v>1.32</v>
@@ -4524,76 +4524,76 @@
         <v>0.11</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="DH9" t="n">
-        <v>108.19</v>
+        <v>107.13</v>
       </c>
       <c r="DI9" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.44</v>
+        <v>4.38</v>
       </c>
       <c r="DL9" t="n">
         <v>0.27</v>
       </c>
       <c r="DM9" t="n">
-        <v>71.72</v>
+        <v>71</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.97</v>
+        <v>11.98</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.33</v>
+        <v>10.46</v>
       </c>
       <c r="DR9" t="n">
         <v>8.08</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.86</v>
+        <v>49.81</v>
       </c>
       <c r="DW9" t="n">
         <v>0.03</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.86</v>
+        <v>11.7</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.47</v>
+        <v>7.38</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.39</v>
+        <v>4.33</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.78</v>
+        <v>17.27</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
         <v>18</v>
@@ -4615,82 +4615,82 @@
         <v>0.11</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="G10" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="H10" t="n">
-        <v>104.06</v>
+        <v>102.16</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="J10" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="K10" t="n">
-        <v>5.11</v>
+        <v>5.05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="M10" t="n">
-        <v>67.56</v>
+        <v>66.42</v>
       </c>
       <c r="N10" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="O10" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>11.06</v>
+        <v>11.16</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.17</v>
+        <v>13.21</v>
       </c>
       <c r="R10" t="n">
-        <v>6.44</v>
+        <v>6.53</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T10" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="V10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>53.39</v>
+        <v>53.32</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.39</v>
+        <v>14.11</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.56</v>
+        <v>9.32</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.83</v>
+        <v>4.79</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.28</v>
+        <v>19.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AF10" t="n">
         <v>0.11</v>
@@ -4774,61 +4774,61 @@
         <v>1.39</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.17</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.44</v>
+        <v>91.89</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>64.86</v>
       </c>
       <c r="BT10" t="n">
-        <v>41.67</v>
+        <v>40.54</v>
       </c>
       <c r="BU10" t="n">
-        <v>22.22</v>
+        <v>21.62</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.11</v>
+        <v>10.81</v>
       </c>
       <c r="BW10" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>48.65</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="BZ10" t="n">
         <v>2.68</v>
@@ -4837,7 +4837,7 @@
         <v>3.21</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CC10" t="n">
         <v>2.77</v>
@@ -4849,7 +4849,7 @@
         <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CG10" t="n">
         <v>2.75</v>
@@ -4861,16 +4861,16 @@
         <v>1.95</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK10" t="n">
         <v>1.83</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CN10" t="n">
         <v>1.54</v>
@@ -4879,10 +4879,10 @@
         <v>1.33</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CR10" t="n">
         <v>1.47</v>
@@ -4900,7 +4900,7 @@
         <v>2.01</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
         <v>1.84</v>
@@ -4912,7 +4912,7 @@
         <v>1.97</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DB10" t="n">
         <v>1.36</v>
@@ -4927,43 +4927,43 @@
         <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="DH10" t="n">
-        <v>104.98</v>
+        <v>103.97</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM10" t="n">
-        <v>63.67</v>
+        <v>63.19</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.64</v>
+        <v>11.68</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.5</v>
+        <v>12.54</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.5</v>
+        <v>7.52</v>
       </c>
       <c r="DS10" t="n">
         <v>0.16</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.39</v>
+        <v>50.44</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.06</v>
+        <v>11.97</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.89</v>
+        <v>7.81</v>
       </c>
       <c r="DZ10" t="n">
         <v>4.16</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.92</v>
+        <v>19.35</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
         <v>0.05</v>
@@ -5099,136 +5099,136 @@
         <v>0.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AI11" t="n">
-        <v>98.29000000000001</v>
+        <v>96.72</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AL11" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>70.28</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="BC11" t="n">
         <v>5.06</v>
       </c>
-      <c r="AM11" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>71.76000000000001</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>12.41</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>7.06</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>48.82</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>14.41</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.12</v>
-      </c>
       <c r="BD11" t="n">
-        <v>18.71</v>
+        <v>17.61</v>
       </c>
       <c r="BE11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF11" t="n">
         <v>1.78</v>
       </c>
-      <c r="BF11" t="n">
-        <v>1.88</v>
-      </c>
       <c r="BG11" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.31</v>
+        <v>9.16</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.86</v>
+        <v>4.78</v>
       </c>
       <c r="BR11" t="n">
-        <v>88.89</v>
+        <v>89.19</v>
       </c>
       <c r="BS11" t="n">
-        <v>69.44</v>
+        <v>70.27</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>51.35</v>
       </c>
       <c r="BU11" t="n">
-        <v>30.56</v>
+        <v>32.43</v>
       </c>
       <c r="BV11" t="n">
-        <v>22.22</v>
+        <v>21.62</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BX11" t="n">
-        <v>52.78</v>
+        <v>54.05</v>
       </c>
       <c r="BY11" t="n">
         <v>2.13</v>
@@ -5240,13 +5240,13 @@
         <v>3.4</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="CC11" t="n">
         <v>2.7</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.79</v>
+        <v>2.92</v>
       </c>
       <c r="CE11" t="n">
         <v>1.36</v>
@@ -5261,7 +5261,7 @@
         <v>1.45</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.67</v>
@@ -5270,10 +5270,10 @@
         <v>1.72</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CN11" t="n">
         <v>1.63</v>
@@ -5285,19 +5285,19 @@
         <v>1.84</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CR11" t="n">
         <v>1.41</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CV11" t="n">
         <v>2.24</v>
@@ -5306,13 +5306,13 @@
         <v>1.71</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA11" t="n">
         <v>1.66</v>
@@ -5321,52 +5321,52 @@
         <v>1.27</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="DE11" t="n">
         <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.91</v>
+        <v>100.08</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.31</v>
+        <v>5.19</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DM11" t="n">
-        <v>71.05</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.75</v>
+        <v>11.57</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.61</v>
+        <v>6.65</v>
       </c>
       <c r="DS11" t="n">
         <v>0.08</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.64</v>
+        <v>50.76</v>
       </c>
       <c r="DW11" t="n">
         <v>0.03</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.75</v>
+        <v>14.62</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.470000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.28</v>
+        <v>5.24</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.45</v>
+        <v>17.92</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
         <v>0.06</v>
@@ -5499,52 +5499,52 @@
         <v>1.61</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AI12" t="n">
-        <v>96.28</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AN12" t="n">
-        <v>63.78</v>
+        <v>63.63</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.67</v>
+        <v>10.16</v>
       </c>
       <c r="AR12" t="n">
-        <v>12</v>
+        <v>11.95</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.33</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AV12" t="n">
         <v>0.11</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>44.06</v>
+        <v>44.16</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.39</v>
+        <v>12.89</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.5</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.89</v>
+        <v>4.79</v>
       </c>
       <c r="BD12" t="n">
-        <v>17.94</v>
+        <v>16.95</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.56</v>
+        <v>9.73</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BL12" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="BO12" t="n">
         <v>1.22</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.19</v>
+        <v>4.27</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.81</v>
+        <v>4.92</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.67</v>
+        <v>91.89</v>
       </c>
       <c r="BS12" t="n">
-        <v>77.78</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>55.56</v>
+        <v>54.05</v>
       </c>
       <c r="BU12" t="n">
-        <v>33.33</v>
+        <v>32.43</v>
       </c>
       <c r="BV12" t="n">
-        <v>25</v>
+        <v>24.32</v>
       </c>
       <c r="BW12" t="n">
-        <v>11.11</v>
+        <v>10.81</v>
       </c>
       <c r="BX12" t="n">
-        <v>69.44</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="BY12" t="n">
         <v>2.79</v>
@@ -5640,31 +5640,31 @@
         <v>2.93</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CB12" t="n">
         <v>3.63</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.54</v>
+        <v>3.49</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF12" t="n">
         <v>2.7</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CH12" t="n">
         <v>1.43</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.72</v>
@@ -5685,7 +5685,7 @@
         <v>1.27</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CQ12" t="n">
         <v>3.09</v>
@@ -5703,10 +5703,10 @@
         <v>1.44</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX12" t="n">
         <v>1.68</v>
@@ -5715,61 +5715,61 @@
         <v>2.1</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DA12" t="n">
         <v>1.73</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC12" t="n">
         <v>1.92</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="DH12" t="n">
-        <v>99.28</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.11</v>
+        <v>4.13</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM12" t="n">
-        <v>63.3</v>
+        <v>63.24</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.56</v>
+        <v>10.78</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.86</v>
+        <v>11.84</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.77</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DS12" t="n">
         <v>0.11</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>44.78</v>
+        <v>44.81</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.56</v>
+        <v>14.27</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.300000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="EA12" t="n">
-        <v>18</v>
+        <v>17.49</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" t="n">
         <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5902,139 +5902,139 @@
         <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="AI13" t="n">
-        <v>105.17</v>
+        <v>106.58</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.39</v>
+        <v>5.53</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="AN13" t="n">
-        <v>74.11</v>
+        <v>76.42</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.44</v>
+        <v>12.53</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.61</v>
+        <v>10.79</v>
       </c>
       <c r="AS13" t="n">
-        <v>9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>55.11</v>
+        <v>55.05</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.11</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.22</v>
+        <v>12.89</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.220000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="BD13" t="n">
-        <v>18.56</v>
+        <v>17.53</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.83</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BO13" t="n">
         <v>1.03</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.94</v>
+        <v>3.81</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.5</v>
+        <v>5.32</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.44</v>
+        <v>94.59</v>
       </c>
       <c r="BS13" t="n">
-        <v>72.22</v>
+        <v>72.97</v>
       </c>
       <c r="BT13" t="n">
-        <v>38.89</v>
+        <v>37.84</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>24.32</v>
       </c>
       <c r="BV13" t="n">
-        <v>13.89</v>
+        <v>13.51</v>
       </c>
       <c r="BW13" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BX13" t="n">
-        <v>52.78</v>
+        <v>51.35</v>
       </c>
       <c r="BY13" t="n">
         <v>1.88</v>
@@ -6043,16 +6043,16 @@
         <v>1.96</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CE13" t="n">
         <v>1.39</v>
@@ -6061,13 +6061,13 @@
         <v>2.79</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CH13" t="n">
         <v>1.41</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.75</v>
@@ -6097,13 +6097,13 @@
         <v>1.43</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV13" t="n">
         <v>2.13</v>
@@ -6112,7 +6112,7 @@
         <v>1.79</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CY13" t="n">
         <v>2.18</v>
@@ -6124,88 +6124,88 @@
         <v>1.67</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="DE13" t="n">
         <v>0.08</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="DH13" t="n">
-        <v>105.92</v>
+        <v>106.62</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.58</v>
+        <v>5.65</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="DM13" t="n">
-        <v>75.94</v>
+        <v>77.08</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.25</v>
+        <v>11.33</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.22</v>
+        <v>11.3</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.56</v>
+        <v>7.54</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.89</v>
+        <v>56.81</v>
       </c>
       <c r="DW13" t="n">
         <v>0.06</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.33</v>
+        <v>10.21</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.16</v>
+        <v>4.08</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.72</v>
+        <v>19.16</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
@@ -1424,10 +1424,10 @@
         <v>10.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.42</v>
+        <v>11.37</v>
       </c>
       <c r="R2" t="n">
-        <v>7.32</v>
+        <v>7.26</v>
       </c>
       <c r="S2" t="n">
         <v>1.16</v>
@@ -1445,25 +1445,25 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>49.05</v>
+        <v>49.53</v>
       </c>
       <c r="Y2" t="n">
         <v>0.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.53</v>
+        <v>13.89</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.630000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.89</v>
+        <v>4.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.47</v>
+        <v>18.68</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE2" t="n">
         <v>1.42</v>
@@ -1736,10 +1736,10 @@
         <v>11.08</v>
       </c>
       <c r="DQ2" t="n">
-        <v>9.890000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DS2" t="n">
         <v>0.05</v>
@@ -1751,25 +1751,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>46.19</v>
+        <v>46.44</v>
       </c>
       <c r="DW2" t="n">
         <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.65</v>
+        <v>12.83</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.130000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.51</v>
+        <v>4.54</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.3</v>
+        <v>18.92</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="EC2" t="n">
         <v>1.92</v>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" t="n">
         <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
         <v>0.06</v>
@@ -1872,139 +1872,139 @@
         <v>1.71</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="n">
-        <v>98.05</v>
+        <v>97.55</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>55.16</v>
+        <v>55.9</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.89</v>
+        <v>10.75</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.58</v>
+        <v>11.95</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.32</v>
+        <v>7.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>46.74</v>
+        <v>47.25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.16</v>
+        <v>11.05</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.26</v>
+        <v>7.15</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>20.26</v>
+        <v>19.2</v>
       </c>
       <c r="BE3" t="n">
         <v>1.38</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="BG3" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.890000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="BO3" t="n">
         <v>1.22</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.31</v>
+        <v>4.16</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.22</v>
+        <v>5.05</v>
       </c>
       <c r="BR3" t="n">
-        <v>97.22</v>
+        <v>97.3</v>
       </c>
       <c r="BS3" t="n">
-        <v>83.33</v>
+        <v>83.78</v>
       </c>
       <c r="BT3" t="n">
-        <v>66.67</v>
+        <v>64.86</v>
       </c>
       <c r="BU3" t="n">
-        <v>41.67</v>
+        <v>40.54</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.11</v>
+        <v>10.81</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>69.44</v>
+        <v>70.27</v>
       </c>
       <c r="BY3" t="n">
         <v>3.25</v>
@@ -2016,13 +2016,13 @@
         <v>3.58</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.57</v>
+        <v>4.48</v>
       </c>
       <c r="CE3" t="n">
         <v>1.35</v>
@@ -2037,19 +2037,19 @@
         <v>1.46</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK3" t="n">
         <v>1.67</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN3" t="n">
         <v>1.7</v>
@@ -2061,7 +2061,7 @@
         <v>1.79</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CR3" t="n">
         <v>1.41</v>
@@ -2085,10 +2085,10 @@
         <v>1.66</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DA3" t="n">
         <v>1.74</v>
@@ -2100,49 +2100,49 @@
         <v>1.85</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="DH3" t="n">
-        <v>103.44</v>
+        <v>103.03</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM3" t="n">
-        <v>60.17</v>
+        <v>60.43</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.19</v>
+        <v>10.13</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.64</v>
+        <v>11.84</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.36</v>
+        <v>7.3</v>
       </c>
       <c r="DS3" t="n">
         <v>0.14</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>47.97</v>
+        <v>48.21</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.72</v>
+        <v>12.62</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.67</v>
+        <v>8.57</v>
       </c>
       <c r="DZ3" t="n">
         <v>4.06</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.36</v>
+        <v>18.81</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="4">
@@ -2230,10 +2230,10 @@
         <v>10.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.16</v>
+        <v>11</v>
       </c>
       <c r="R4" t="n">
-        <v>7</v>
+        <v>7.05</v>
       </c>
       <c r="S4" t="n">
         <v>1.05</v>
@@ -2257,19 +2257,19 @@
         <v>0.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.58</v>
+        <v>11.79</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.16</v>
+        <v>7.32</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="AC4" t="n">
-        <v>16</v>
+        <v>16.89</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE4" t="n">
         <v>1.53</v>
@@ -2359,7 +2359,7 @@
         <v>2.73</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.59</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI4" t="n">
         <v>2.73</v>
@@ -2542,10 +2542,10 @@
         <v>10.76</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10.06</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.97</v>
+        <v>8</v>
       </c>
       <c r="DS4" t="n">
         <v>0.19</v>
@@ -2563,19 +2563,19 @@
         <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.33</v>
+        <v>11.43</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.05</v>
+        <v>7.14</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.27</v>
+        <v>4.29</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.78</v>
+        <v>17.24</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="EC4" t="n">
         <v>1.65</v>
@@ -2615,7 +2615,7 @@
         <v>1.84</v>
       </c>
       <c r="K5" t="n">
-        <v>5.79</v>
+        <v>5.74</v>
       </c>
       <c r="L5" t="n">
         <v>0.37</v>
@@ -2633,10 +2633,10 @@
         <v>8.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.79</v>
+        <v>11.68</v>
       </c>
       <c r="R5" t="n">
-        <v>5.68</v>
+        <v>5.63</v>
       </c>
       <c r="S5" t="n">
         <v>1.47</v>
@@ -2654,25 +2654,25 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55.95</v>
+        <v>56.11</v>
       </c>
       <c r="Y5" t="n">
         <v>0.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.68</v>
+        <v>17.84</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.84</v>
+        <v>12.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.84</v>
+        <v>5.79</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.53</v>
+        <v>19.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AE5" t="n">
         <v>1.79</v>
@@ -2762,7 +2762,7 @@
         <v>2.68</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.890000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI5" t="n">
         <v>2.68</v>
@@ -2927,7 +2927,7 @@
         <v>1.73</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.6</v>
+        <v>5.57</v>
       </c>
       <c r="DL5" t="n">
         <v>0.38</v>
@@ -2945,10 +2945,10 @@
         <v>9.73</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.84</v>
+        <v>10.78</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.4</v>
+        <v>6.38</v>
       </c>
       <c r="DS5" t="n">
         <v>0.09</v>
@@ -2960,22 +2960,22 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.24</v>
+        <v>54.32</v>
       </c>
       <c r="DW5" t="n">
         <v>0.03</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.59</v>
+        <v>15.68</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.46</v>
+        <v>10.57</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.13</v>
+        <v>5.11</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.41</v>
+        <v>19.14</v>
       </c>
       <c r="EB5" t="n">
         <v>1.84</v>
@@ -3099,7 +3099,7 @@
         <v>2.42</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="AM6" t="n">
         <v>0.37</v>
@@ -3144,19 +3144,19 @@
         <v>0.16</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.42</v>
+        <v>9.68</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.21</v>
+        <v>6.47</v>
       </c>
       <c r="BC6" t="n">
         <v>3.21</v>
       </c>
       <c r="BD6" t="n">
-        <v>16.79</v>
+        <v>17.95</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="BF6" t="n">
         <v>2.16</v>
@@ -3165,7 +3165,7 @@
         <v>2.08</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.619999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="BI6" t="n">
         <v>2.08</v>
@@ -3330,7 +3330,7 @@
         <v>2.08</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="DL6" t="n">
         <v>0.38</v>
@@ -3369,19 +3369,19 @@
         <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.22</v>
+        <v>10.35</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.43</v>
+        <v>6.57</v>
       </c>
       <c r="DZ6" t="n">
         <v>3.78</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.51</v>
+        <v>19.11</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="EC6" t="n">
         <v>1.95</v>
@@ -3439,7 +3439,7 @@
         <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>14</v>
+        <v>13.84</v>
       </c>
       <c r="R7" t="n">
         <v>7.11</v>
@@ -3460,25 +3460,25 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>50.26</v>
+        <v>50</v>
       </c>
       <c r="Y7" t="n">
         <v>0.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>12</v>
+        <v>12.16</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.210000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="AB7" t="n">
         <v>3.79</v>
       </c>
       <c r="AC7" t="n">
-        <v>15.95</v>
+        <v>16.89</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE7" t="n">
         <v>1.68</v>
@@ -3568,7 +3568,7 @@
         <v>2.16</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.109999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI7" t="n">
         <v>2.16</v>
@@ -3751,7 +3751,7 @@
         <v>10.21</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.49</v>
+        <v>12.4</v>
       </c>
       <c r="DR7" t="n">
         <v>7.65</v>
@@ -3766,25 +3766,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.64</v>
+        <v>48.51</v>
       </c>
       <c r="DW7" t="n">
         <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.81</v>
+        <v>10.9</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.13</v>
+        <v>7.22</v>
       </c>
       <c r="DZ7" t="n">
         <v>3.68</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.7</v>
+        <v>17.19</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="EC7" t="n">
         <v>2.03</v>
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
         <v>19</v>
@@ -3809,49 +3809,49 @@
         <v>0.06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="G8" t="n">
-        <v>2.41</v>
+        <v>2.22</v>
       </c>
       <c r="H8" t="n">
-        <v>94.81999999999999</v>
+        <v>93.94</v>
       </c>
       <c r="I8" t="n">
         <v>0.06</v>
       </c>
       <c r="J8" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="L8" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>61.94</v>
+        <v>61.17</v>
       </c>
       <c r="N8" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="O8" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>11.94</v>
+        <v>12</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.24</v>
+        <v>12.22</v>
       </c>
       <c r="R8" t="n">
-        <v>7.06</v>
+        <v>7.17</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="U8" t="n">
         <v>0.06</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.88</v>
+        <v>51.39</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.53</v>
+        <v>13.11</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.24</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.29</v>
+        <v>4.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.41</v>
+        <v>21.11</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,64 +3968,64 @@
         <v>1.74</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.220000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="BO8" t="n">
         <v>0.78</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.81</v>
+        <v>3.68</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.08</v>
+        <v>4.92</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.67</v>
+        <v>91.89</v>
       </c>
       <c r="BS8" t="n">
-        <v>72.22</v>
+        <v>72.97</v>
       </c>
       <c r="BT8" t="n">
-        <v>47.22</v>
+        <v>45.95</v>
       </c>
       <c r="BU8" t="n">
-        <v>25</v>
+        <v>24.32</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BX8" t="n">
-        <v>55.56</v>
+        <v>56.76</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="CA8" t="n">
         <v>3.31</v>
@@ -4040,10 +4040,10 @@
         <v>3.97</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CG8" t="n">
         <v>2.82</v>
@@ -4052,19 +4052,19 @@
         <v>1.38</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL8" t="n">
         <v>2.25</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN8" t="n">
         <v>1.66</v>
@@ -4073,10 +4073,10 @@
         <v>1.31</v>
       </c>
       <c r="CP8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="CR8" t="n">
         <v>1.44</v>
@@ -4091,16 +4091,16 @@
         <v>1.41</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CW8" t="n">
         <v>1.83</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.1</v>
@@ -4109,55 +4109,55 @@
         <v>1.69</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="DE8" t="n">
         <v>0.03</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="DH8" t="n">
-        <v>97.89</v>
+        <v>97.38</v>
       </c>
       <c r="DI8" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DM8" t="n">
-        <v>60.33</v>
+        <v>60</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.86</v>
+        <v>11.89</v>
       </c>
       <c r="DQ8" t="n">
         <v>11.7</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.2</v>
+        <v>7.25</v>
       </c>
       <c r="DS8" t="n">
         <v>0.09</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51</v>
+        <v>50.78</v>
       </c>
       <c r="DW8" t="n">
         <v>0.22</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.66</v>
+        <v>12.48</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.470000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.3</v>
+        <v>19.73</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="9">
@@ -4347,25 +4347,25 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46.83</v>
+        <v>47.28</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.22</v>
+        <v>10.44</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.67</v>
+        <v>6.89</v>
       </c>
       <c r="BC9" t="n">
         <v>3.56</v>
       </c>
       <c r="BD9" t="n">
-        <v>15.39</v>
+        <v>16.39</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BF9" t="n">
         <v>2.67</v>
@@ -4572,25 +4572,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.81</v>
+        <v>50.03</v>
       </c>
       <c r="DW9" t="n">
         <v>0.03</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.7</v>
+        <v>11.81</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.38</v>
+        <v>7.49</v>
       </c>
       <c r="DZ9" t="n">
         <v>4.33</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.27</v>
+        <v>17.76</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="EC9" t="n">
         <v>2.24</v>
@@ -4648,7 +4648,7 @@
         <v>11.16</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.21</v>
+        <v>13.16</v>
       </c>
       <c r="R10" t="n">
         <v>6.53</v>
@@ -4669,25 +4669,25 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>53.32</v>
+        <v>52.89</v>
       </c>
       <c r="Y10" t="n">
         <v>0.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.11</v>
+        <v>14.32</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.32</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AB10" t="n">
         <v>4.79</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.16</v>
+        <v>20.11</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE10" t="n">
         <v>1.47</v>
@@ -4960,7 +4960,7 @@
         <v>11.68</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.54</v>
+        <v>12.51</v>
       </c>
       <c r="DR10" t="n">
         <v>7.52</v>
@@ -4975,25 +4975,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.44</v>
+        <v>50.21</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.97</v>
+        <v>12.08</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.81</v>
+        <v>7.92</v>
       </c>
       <c r="DZ10" t="n">
         <v>4.16</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.35</v>
+        <v>19.84</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="EC10" t="n">
         <v>1.43</v>
@@ -5132,10 +5132,10 @@
         <v>12</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.83</v>
+        <v>7.89</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.11</v>
+        <v>7.17</v>
       </c>
       <c r="AT11" t="n">
         <v>1.44</v>
@@ -5153,25 +5153,25 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>49.17</v>
+        <v>49</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>14.17</v>
+        <v>14.28</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.109999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BC11" t="n">
         <v>5.06</v>
       </c>
       <c r="BD11" t="n">
-        <v>17.61</v>
+        <v>18.61</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BF11" t="n">
         <v>1.78</v>
@@ -5180,7 +5180,7 @@
         <v>2.73</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.16</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI11" t="n">
         <v>2.73</v>
@@ -5363,10 +5363,10 @@
         <v>11.57</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.029999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.65</v>
+        <v>6.68</v>
       </c>
       <c r="DS11" t="n">
         <v>0.08</v>
@@ -5378,22 +5378,22 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.76</v>
+        <v>50.67</v>
       </c>
       <c r="DW11" t="n">
         <v>0.03</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.62</v>
+        <v>14.68</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.380000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="DZ11" t="n">
         <v>5.24</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.92</v>
+        <v>18.4</v>
       </c>
       <c r="EB11" t="n">
         <v>1.8</v>
@@ -5556,25 +5556,25 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>44.16</v>
+        <v>43.68</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.89</v>
+        <v>13.32</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.109999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BC12" t="n">
         <v>4.79</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.95</v>
+        <v>17.84</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BF12" t="n">
         <v>1.74</v>
@@ -5781,25 +5781,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>44.81</v>
+        <v>44.57</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.27</v>
+        <v>14.49</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.08</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ12" t="n">
         <v>5.19</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.49</v>
+        <v>17.95</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="EC12" t="n">
         <v>1.68</v>
@@ -5920,7 +5920,7 @@
         <v>2.21</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.53</v>
+        <v>5.58</v>
       </c>
       <c r="AM13" t="n">
         <v>0.16</v>
@@ -5938,7 +5938,7 @@
         <v>12.53</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.79</v>
+        <v>10.74</v>
       </c>
       <c r="AS13" t="n">
         <v>8.890000000000001</v>
@@ -5959,25 +5959,25 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>55.05</v>
+        <v>55.32</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.11</v>
       </c>
       <c r="BA13" t="n">
-        <v>12.89</v>
+        <v>13.21</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.050000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="BC13" t="n">
         <v>3.84</v>
       </c>
       <c r="BD13" t="n">
-        <v>17.53</v>
+        <v>18.58</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="BF13" t="n">
         <v>2.11</v>
@@ -5986,7 +5986,7 @@
         <v>2.46</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.779999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="BI13" t="n">
         <v>2.46</v>
@@ -6151,7 +6151,7 @@
         <v>2.03</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.65</v>
+        <v>5.68</v>
       </c>
       <c r="DL13" t="n">
         <v>0.35</v>
@@ -6169,7 +6169,7 @@
         <v>11.33</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.3</v>
+        <v>11.27</v>
       </c>
       <c r="DR13" t="n">
         <v>7.54</v>
@@ -6184,25 +6184,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.81</v>
+        <v>56.95</v>
       </c>
       <c r="DW13" t="n">
         <v>0.06</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.3</v>
+        <v>14.46</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.21</v>
+        <v>10.38</v>
       </c>
       <c r="DZ13" t="n">
         <v>4.08</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.16</v>
+        <v>19.7</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="EC13" t="n">
         <v>1.97</v>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
@@ -1890,7 +1890,7 @@
         <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AM3" t="n">
         <v>0.4</v>
@@ -1908,10 +1908,10 @@
         <v>10.75</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.95</v>
+        <v>11.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.2</v>
+        <v>7.25</v>
       </c>
       <c r="AT3" t="n">
         <v>2.05</v>
@@ -1929,25 +1929,25 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>47.25</v>
+        <v>47.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.05</v>
+        <v>11.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.15</v>
+        <v>7.5</v>
       </c>
       <c r="BC3" t="n">
         <v>3.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.2</v>
+        <v>20.65</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BF3" t="n">
         <v>1.55</v>
@@ -1956,7 +1956,7 @@
         <v>2.97</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.84</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI3" t="n">
         <v>2.97</v>
@@ -2121,7 +2121,7 @@
         <v>1.73</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="DL3" t="n">
         <v>0.35</v>
@@ -2139,10 +2139,10 @@
         <v>10.13</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.84</v>
+        <v>11.76</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.3</v>
+        <v>7.32</v>
       </c>
       <c r="DS3" t="n">
         <v>0.14</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>48.21</v>
+        <v>48.3</v>
       </c>
       <c r="DW3" t="n">
         <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.62</v>
+        <v>12.81</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.57</v>
+        <v>8.76</v>
       </c>
       <c r="DZ3" t="n">
         <v>4.06</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.81</v>
+        <v>19.59</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="EC3" t="n">
         <v>1.62</v>
@@ -3863,25 +3863,25 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.39</v>
+        <v>51.22</v>
       </c>
       <c r="Y8" t="n">
         <v>0.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.11</v>
+        <v>13.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.890000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AB8" t="n">
         <v>4.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.11</v>
+        <v>22.22</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE8" t="n">
         <v>1.94</v>
@@ -3971,7 +3971,7 @@
         <v>2.49</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.19</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI8" t="n">
         <v>2.49</v>
@@ -4169,25 +4169,25 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.78</v>
+        <v>50.7</v>
       </c>
       <c r="DW8" t="n">
         <v>0.22</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.48</v>
+        <v>12.59</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.33</v>
+        <v>8.43</v>
       </c>
       <c r="DZ8" t="n">
         <v>4.16</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.73</v>
+        <v>20.27</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="EC8" t="n">
         <v>1.84</v>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2" t="n">
         <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
         <v>0.05</v>
@@ -1469,139 +1469,139 @@
         <v>1.42</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>93.83</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="AN2" t="n">
-        <v>58.44</v>
+        <v>57.58</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.94</v>
+        <v>12.11</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.279999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.56</v>
+        <v>10.58</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>43.17</v>
+        <v>42.74</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.72</v>
+        <v>11.42</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.61</v>
+        <v>7.32</v>
       </c>
       <c r="BC2" t="n">
         <v>4.11</v>
       </c>
       <c r="BD2" t="n">
-        <v>19.17</v>
+        <v>18.11</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.460000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.86</v>
+        <v>4.03</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.08</v>
+        <v>5.03</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.59</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>72.97</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>54.05</v>
+        <v>55.26</v>
       </c>
       <c r="BU2" t="n">
-        <v>21.62</v>
+        <v>23.68</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.41</v>
+        <v>5.26</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>59.46</v>
+        <v>60.53</v>
       </c>
       <c r="BY2" t="n">
         <v>2.8</v>
@@ -1610,16 +1610,16 @@
         <v>3.06</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CB2" t="n">
         <v>3.43</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.61</v>
+        <v>3.55</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="CE2" t="n">
         <v>1.43</v>
@@ -1628,7 +1628,7 @@
         <v>2.95</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CH2" t="n">
         <v>1.37</v>
@@ -1640,25 +1640,25 @@
         <v>1.82</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO2" t="n">
         <v>1.33</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CR2" t="n">
         <v>1.47</v>
@@ -1673,73 +1673,73 @@
         <v>1.38</v>
       </c>
       <c r="CV2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX2" t="n">
         <v>1.77</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB2" t="n">
         <v>1.35</v>
       </c>
       <c r="DC2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
         <v>2.13</v>
       </c>
-      <c r="DD2" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>99.81</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>2.08</v>
-      </c>
       <c r="DK2" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="DM2" t="n">
-        <v>64.08</v>
+        <v>63.5</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.08</v>
+        <v>11.18</v>
       </c>
       <c r="DQ2" t="n">
-        <v>9.869999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.869999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="DS2" t="n">
         <v>0.05</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>46.44</v>
+        <v>46.14</v>
       </c>
       <c r="DW2" t="n">
         <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.83</v>
+        <v>12.66</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.92</v>
+        <v>18.4</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
         <v>20</v>
@@ -1797,79 +1797,79 @@
         <v>1.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="H3" t="n">
-        <v>109.47</v>
+        <v>110.67</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="K3" t="n">
-        <v>5.06</v>
+        <v>5.33</v>
       </c>
       <c r="L3" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>65.76000000000001</v>
+        <v>68</v>
       </c>
       <c r="N3" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="O3" t="n">
-        <v>1.59</v>
+        <v>1.94</v>
       </c>
       <c r="P3" t="n">
-        <v>9.41</v>
+        <v>9.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.71</v>
+        <v>12.11</v>
       </c>
       <c r="R3" t="n">
-        <v>7.41</v>
+        <v>7.17</v>
       </c>
       <c r="S3" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T3" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="U3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>49.35</v>
+        <v>50.22</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.47</v>
+        <v>14.56</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.24</v>
+        <v>10</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.24</v>
+        <v>4.56</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.35</v>
+        <v>17.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AF3" t="n">
         <v>0.1</v>
@@ -1953,70 +1953,70 @@
         <v>1.55</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.859999999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="BL3" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="BN3" t="n">
         <v>1.76</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.16</v>
+        <v>4.32</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="BR3" t="n">
-        <v>97.3</v>
+        <v>97.37</v>
       </c>
       <c r="BS3" t="n">
-        <v>83.78</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>64.86</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="BU3" t="n">
-        <v>40.54</v>
+        <v>42.11</v>
       </c>
       <c r="BV3" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>70.27</v>
+        <v>71.05</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.48</v>
+        <v>3.41</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC3" t="n">
         <v>4.11</v>
@@ -2031,7 +2031,7 @@
         <v>2.64</v>
       </c>
       <c r="CG3" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CH3" t="n">
         <v>1.46</v>
@@ -2046,13 +2046,13 @@
         <v>1.67</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CM3" t="n">
         <v>2.16</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO3" t="n">
         <v>1.24</v>
@@ -2079,7 +2079,7 @@
         <v>2.17</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX3" t="n">
         <v>1.66</v>
@@ -2109,73 +2109,73 @@
         <v>1.08</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DH3" t="n">
-        <v>103.03</v>
+        <v>103.76</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM3" t="n">
-        <v>60.43</v>
+        <v>61.63</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.13</v>
+        <v>10.24</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.76</v>
+        <v>11.95</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.32</v>
+        <v>7.21</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>48.3</v>
+        <v>48.74</v>
       </c>
       <c r="DW3" t="n">
         <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.81</v>
+        <v>12.9</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.76</v>
+        <v>8.68</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.06</v>
+        <v>4.21</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.59</v>
+        <v>19.05</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
         <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
         <v>0.05</v>
@@ -2275,139 +2275,139 @@
         <v>1.53</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AI4" t="n">
-        <v>94.78</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AK4" t="n">
         <v>1.89</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AN4" t="n">
-        <v>61.17</v>
+        <v>60.32</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.5</v>
+        <v>11.32</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.890000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>9</v>
+        <v>9.32</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>48.56</v>
+        <v>48.11</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.11</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.06</v>
+        <v>10.79</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.94</v>
+        <v>6.63</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.11</v>
+        <v>4.16</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.61</v>
+        <v>16.63</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.619999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BO4" t="n">
         <v>0.95</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.97</v>
+        <v>4.11</v>
       </c>
       <c r="BR4" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS4" t="n">
-        <v>81.08</v>
+        <v>81.58</v>
       </c>
       <c r="BT4" t="n">
-        <v>54.05</v>
+        <v>55.26</v>
       </c>
       <c r="BU4" t="n">
-        <v>35.14</v>
+        <v>34.21</v>
       </c>
       <c r="BV4" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>62.16</v>
+        <v>60.53</v>
       </c>
       <c r="BY4" t="n">
         <v>2.38</v>
@@ -2422,16 +2422,16 @@
         <v>3.5</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="CE4" t="n">
         <v>1.39</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CG4" t="n">
         <v>2.85</v>
@@ -2446,7 +2446,7 @@
         <v>1.76</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CL4" t="n">
         <v>2.48</v>
@@ -2464,13 +2464,13 @@
         <v>1.95</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CR4" t="n">
         <v>1.45</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CT4" t="n">
         <v>2.88</v>
@@ -2479,106 +2479,106 @@
         <v>1.4</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DA4" t="n">
         <v>1.58</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="DH4" t="n">
-        <v>107.35</v>
+        <v>107.29</v>
       </c>
       <c r="DI4" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM4" t="n">
-        <v>65.59999999999999</v>
+        <v>65.06</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.76</v>
+        <v>10.68</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="DR4" t="n">
-        <v>8</v>
+        <v>8.18</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>50.73</v>
+        <v>50.45</v>
       </c>
       <c r="DW4" t="n">
         <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.43</v>
+        <v>11.29</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.14</v>
+        <v>6.98</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.29</v>
+        <v>4.32</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.24</v>
+        <v>16.76</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" t="n">
         <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
         <v>0.05</v>
@@ -2678,139 +2678,139 @@
         <v>1.79</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="AI5" t="n">
-        <v>98.56</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.39</v>
+        <v>5.37</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>67.28</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.78</v>
+        <v>10.79</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.17</v>
+        <v>6.95</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52.44</v>
+        <v>52.53</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.39</v>
+        <v>13.79</v>
       </c>
       <c r="BB5" t="n">
-        <v>9</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.39</v>
+        <v>4.74</v>
       </c>
       <c r="BD5" t="n">
-        <v>18.28</v>
+        <v>17.26</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BG5" t="n">
         <v>2.68</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.859999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="BI5" t="n">
         <v>2.68</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.65</v>
+        <v>3.53</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.76</v>
+        <v>4.61</v>
       </c>
       <c r="BR5" t="n">
-        <v>86.48999999999999</v>
+        <v>86.84</v>
       </c>
       <c r="BS5" t="n">
-        <v>67.56999999999999</v>
+        <v>68.42</v>
       </c>
       <c r="BT5" t="n">
-        <v>48.65</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>35.14</v>
+        <v>34.21</v>
       </c>
       <c r="BV5" t="n">
-        <v>18.92</v>
+        <v>18.42</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.41</v>
+        <v>5.26</v>
       </c>
       <c r="BX5" t="n">
-        <v>62.16</v>
+        <v>63.16</v>
       </c>
       <c r="BY5" t="n">
         <v>1.96</v>
@@ -2825,7 +2825,7 @@
         <v>3.51</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="CD5" t="n">
         <v>2.37</v>
@@ -2834,25 +2834,25 @@
         <v>1.44</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.85</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CM5" t="n">
         <v>1.99</v>
@@ -2864,19 +2864,19 @@
         <v>1.34</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="CR5" t="n">
         <v>1.47</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CU5" t="n">
         <v>1.39</v>
@@ -2885,7 +2885,7 @@
         <v>1.96</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX5" t="n">
         <v>1.78</v>
@@ -2894,7 +2894,7 @@
         <v>2.22</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DA5" t="n">
         <v>1.64</v>
@@ -2906,7 +2906,7 @@
         <v>2.16</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="DE5" t="n">
         <v>0.05</v>
@@ -2915,46 +2915,46 @@
         <v>1.16</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="DH5" t="n">
-        <v>102.06</v>
+        <v>101.82</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.57</v>
+        <v>5.56</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="DM5" t="n">
-        <v>68.11</v>
+        <v>68.55</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="DP5" t="n">
-        <v>9.73</v>
+        <v>9.76</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.78</v>
+        <v>10.76</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.38</v>
+        <v>6.29</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
@@ -2963,25 +2963,25 @@
         <v>54.32</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.68</v>
+        <v>15.82</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.57</v>
+        <v>10.55</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.11</v>
+        <v>5.26</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.14</v>
+        <v>18.6</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
         <v>19</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="H6" t="n">
-        <v>95.11</v>
+        <v>98</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="K6" t="n">
-        <v>4.94</v>
+        <v>4.79</v>
       </c>
       <c r="L6" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>60.28</v>
+        <v>61.42</v>
       </c>
       <c r="N6" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="P6" t="n">
-        <v>10.17</v>
+        <v>10.11</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.39</v>
+        <v>11.63</v>
       </c>
       <c r="R6" t="n">
-        <v>5.83</v>
+        <v>5.89</v>
       </c>
       <c r="S6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.94</v>
+        <v>51</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.06</v>
+        <v>11</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.67</v>
+        <v>6.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.33</v>
+        <v>19.21</v>
       </c>
       <c r="AD6" t="n">
         <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AF6" t="n">
         <v>0.11</v>
@@ -3162,70 +3162,70 @@
         <v>2.16</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.65</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.24</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.41</v>
+        <v>3.29</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.43</v>
+        <v>4.29</v>
       </c>
       <c r="BR6" t="n">
-        <v>83.78</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>56.76</v>
+        <v>55.26</v>
       </c>
       <c r="BT6" t="n">
-        <v>40.54</v>
+        <v>39.47</v>
       </c>
       <c r="BU6" t="n">
-        <v>18.92</v>
+        <v>18.42</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.41</v>
+        <v>5.26</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BX6" t="n">
-        <v>40.54</v>
+        <v>39.47</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="CA6" t="n">
         <v>3.13</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CC6" t="n">
         <v>3.22</v>
@@ -3276,7 +3276,7 @@
         <v>1.5</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CT6" t="n">
         <v>2.69</v>
@@ -3285,19 +3285,19 @@
         <v>1.36</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CX6" t="n">
         <v>1.88</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DA6" t="n">
         <v>1.56</v>
@@ -3312,79 +3312,79 @@
         <v>4.18</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="DH6" t="n">
-        <v>94.62</v>
+        <v>96.08</v>
       </c>
       <c r="DI6" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.38</v>
+        <v>4.32</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="DM6" t="n">
-        <v>56.76</v>
+        <v>57.42</v>
       </c>
       <c r="DN6" t="n">
         <v>0.78</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.62</v>
+        <v>11.56</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.22</v>
+        <v>11.34</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.16</v>
+        <v>7.15</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.57</v>
+        <v>48.66</v>
       </c>
       <c r="DW6" t="n">
         <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.35</v>
+        <v>10.34</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.11</v>
+        <v>18.58</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" t="n">
         <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
         <v>0.11</v>
@@ -3484,139 +3484,139 @@
         <v>1.68</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AI7" t="n">
-        <v>96.61</v>
+        <v>96.47</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.22</v>
+        <v>4.37</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="AN7" t="n">
-        <v>57.61</v>
+        <v>57.79</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.44</v>
+        <v>10.68</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.89</v>
+        <v>11.16</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.220000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AU7" t="n">
         <v>0.89</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>46.94</v>
+        <v>46.84</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.56</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>5.79</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.5</v>
+        <v>16.53</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.140000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BN7" t="n">
         <v>1.24</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BP7" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="BR7" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS7" t="n">
-        <v>59.46</v>
+        <v>57.89</v>
       </c>
       <c r="BT7" t="n">
-        <v>37.84</v>
+        <v>36.84</v>
       </c>
       <c r="BU7" t="n">
-        <v>16.22</v>
+        <v>15.79</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.109999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BX7" t="n">
-        <v>43.24</v>
+        <v>42.11</v>
       </c>
       <c r="BY7" t="n">
         <v>2.43</v>
@@ -3628,22 +3628,22 @@
         <v>3.14</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CC7" t="n">
         <v>3.1</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.21</v>
+        <v>3.29</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CH7" t="n">
         <v>1.33</v>
@@ -3655,13 +3655,13 @@
         <v>1.93</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CN7" t="n">
         <v>1.54</v>
@@ -3673,88 +3673,88 @@
         <v>2.2</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CU7" t="n">
         <v>1.35</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DB7" t="n">
         <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.41</v>
+        <v>4.37</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="DG7" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="DH7" t="n">
-        <v>104.84</v>
+        <v>104.55</v>
       </c>
       <c r="DI7" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="DM7" t="n">
-        <v>67.76000000000001</v>
+        <v>67.58</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.21</v>
+        <v>10.34</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.65</v>
+        <v>7.76</v>
       </c>
       <c r="DS7" t="n">
         <v>0.16</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.51</v>
+        <v>48.42</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.9</v>
+        <v>10.76</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.22</v>
+        <v>7.08</v>
       </c>
       <c r="DZ7" t="n">
         <v>3.68</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.19</v>
+        <v>16.71</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
         <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
         <v>0.06</v>
@@ -3890,136 +3890,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" t="n">
-        <v>100.63</v>
+        <v>101.6</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="AN8" t="n">
-        <v>58.89</v>
+        <v>59</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.79</v>
+        <v>11.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.21</v>
+        <v>11.45</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.32</v>
+        <v>7.25</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>50.21</v>
+        <v>50.15</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.89</v>
+        <v>11.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.79</v>
+        <v>7.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.42</v>
+        <v>17.45</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.220000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="BM8" t="n">
         <v>0.76</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.68</v>
+        <v>3.63</v>
       </c>
       <c r="BQ8" t="n">
         <v>4.92</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS8" t="n">
-        <v>72.97</v>
+        <v>71.05</v>
       </c>
       <c r="BT8" t="n">
-        <v>45.95</v>
+        <v>44.74</v>
       </c>
       <c r="BU8" t="n">
-        <v>24.32</v>
+        <v>23.68</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.109999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BX8" t="n">
-        <v>56.76</v>
+        <v>55.26</v>
       </c>
       <c r="BY8" t="n">
         <v>2.74</v>
@@ -4028,31 +4028,31 @@
         <v>2.99</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CB8" t="n">
         <v>3.54</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="CE8" t="n">
         <v>1.4</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CH8" t="n">
         <v>1.38</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.78</v>
@@ -4067,22 +4067,22 @@
         <v>2.09</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CR8" t="n">
         <v>1.44</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CT8" t="n">
         <v>2.91</v>
@@ -4091,10 +4091,10 @@
         <v>1.41</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX8" t="n">
         <v>1.72</v>
@@ -4103,94 +4103,94 @@
         <v>2.14</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DB8" t="n">
         <v>1.32</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="DE8" t="n">
         <v>0.03</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="DH8" t="n">
-        <v>97.38</v>
+        <v>97.97</v>
       </c>
       <c r="DI8" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM8" t="n">
-        <v>60</v>
+        <v>60.03</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DP8" t="n">
         <v>11.89</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.7</v>
+        <v>11.81</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.25</v>
+        <v>7.21</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.7</v>
+        <v>50.66</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.59</v>
+        <v>12.31</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.43</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.27</v>
+        <v>19.71</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="9">
@@ -4200,25 +4200,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
         <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="H9" t="n">
-        <v>118.79</v>
+        <v>117.6</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4227,67 +4227,67 @@
         <v>1.95</v>
       </c>
       <c r="K9" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="M9" t="n">
-        <v>83.79000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>10.74</v>
+        <v>10.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.21</v>
+        <v>10.4</v>
       </c>
       <c r="R9" t="n">
-        <v>6.47</v>
+        <v>6.75</v>
       </c>
       <c r="S9" t="n">
         <v>1.05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U9" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>52.63</v>
+        <v>52.3</v>
       </c>
       <c r="Y9" t="n">
         <v>0.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.11</v>
+        <v>12.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.050000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.05</v>
+        <v>18.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
         <v>0.06</v>
@@ -4371,67 +4371,67 @@
         <v>2.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.619999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.32</v>
+        <v>3.21</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.05</v>
+        <v>4.89</v>
       </c>
       <c r="BR9" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS9" t="n">
-        <v>75.68000000000001</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>48.65</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>27.03</v>
+        <v>26.32</v>
       </c>
       <c r="BV9" t="n">
-        <v>8.109999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>54.05</v>
+        <v>55.26</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CB9" t="n">
         <v>3.57</v>
@@ -4446,25 +4446,25 @@
         <v>1.39</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CH9" t="n">
         <v>1.41</v>
       </c>
       <c r="CI9" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK9" t="n">
         <v>1.74</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CM9" t="n">
         <v>2.02</v>
@@ -4476,10 +4476,10 @@
         <v>1.29</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CR9" t="n">
         <v>1.44</v>
@@ -4518,79 +4518,79 @@
         <v>2.02</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="DE9" t="n">
         <v>0.11</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="DH9" t="n">
-        <v>107.13</v>
+        <v>106.81</v>
       </c>
       <c r="DI9" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="DM9" t="n">
-        <v>71</v>
+        <v>71.03</v>
       </c>
       <c r="DN9" t="n">
         <v>0.71</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.98</v>
+        <v>11.9</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.46</v>
+        <v>10.55</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.08</v>
+        <v>8.19</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.03</v>
+        <v>49.92</v>
       </c>
       <c r="DW9" t="n">
         <v>0.03</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.81</v>
+        <v>11.68</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.49</v>
+        <v>7.37</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.76</v>
+        <v>17.26</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="EC9" t="n">
         <v>2.24</v>
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
         <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
         <v>0.11</v>
@@ -4696,49 +4696,49 @@
         <v>0.11</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AI10" t="n">
-        <v>105.89</v>
+        <v>107.21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.72</v>
+        <v>3.63</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="AN10" t="n">
-        <v>59.78</v>
+        <v>60.21</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.22</v>
+        <v>12.37</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.83</v>
+        <v>11.74</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.56</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AV10" t="n">
         <v>0.11</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>47.39</v>
+        <v>47.42</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.11</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.720000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.22</v>
+        <v>6.05</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.56</v>
+        <v>18.47</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.109999999999999</v>
+        <v>8</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.27</v>
+        <v>3.16</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.32</v>
+        <v>4.18</v>
       </c>
       <c r="BR10" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS10" t="n">
-        <v>64.86</v>
+        <v>63.16</v>
       </c>
       <c r="BT10" t="n">
-        <v>40.54</v>
+        <v>39.47</v>
       </c>
       <c r="BU10" t="n">
-        <v>21.62</v>
+        <v>21.05</v>
       </c>
       <c r="BV10" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="BW10" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BX10" t="n">
-        <v>48.65</v>
+        <v>47.37</v>
       </c>
       <c r="BY10" t="n">
         <v>2.51</v>
@@ -4837,22 +4837,22 @@
         <v>3.21</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH10" t="n">
         <v>1.37</v>
@@ -4879,7 +4879,7 @@
         <v>1.33</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CQ10" t="n">
         <v>3.62</v>
@@ -4891,25 +4891,25 @@
         <v>3.19</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV10" t="n">
         <v>2.01</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DA10" t="n">
         <v>1.58</v>
@@ -4918,10 +4918,10 @@
         <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="DE10" t="n">
         <v>0.11</v>
@@ -4930,40 +4930,40 @@
         <v>0.87</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="DH10" t="n">
-        <v>103.97</v>
+        <v>104.68</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.4</v>
+        <v>4.34</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="DM10" t="n">
-        <v>63.19</v>
+        <v>63.32</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.68</v>
+        <v>11.76</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.51</v>
+        <v>12.45</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.52</v>
+        <v>7.58</v>
       </c>
       <c r="DS10" t="n">
         <v>0.16</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.21</v>
+        <v>50.15</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.08</v>
+        <v>11.92</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.92</v>
+        <v>7.79</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.16</v>
+        <v>4.13</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.84</v>
+        <v>19.29</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="11">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
         <v>18</v>
@@ -5018,82 +5018,82 @@
         <v>0.05</v>
       </c>
       <c r="F11" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="G11" t="n">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="H11" t="n">
-        <v>103.26</v>
+        <v>106.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="K11" t="n">
-        <v>5.53</v>
+        <v>5.8</v>
       </c>
       <c r="L11" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="M11" t="n">
-        <v>70.42</v>
+        <v>71.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>11.16</v>
+        <v>10.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.16</v>
+        <v>10.1</v>
       </c>
       <c r="R11" t="n">
-        <v>6.21</v>
+        <v>6</v>
       </c>
       <c r="S11" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="T11" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="U11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="V11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>52.26</v>
+        <v>52.65</v>
       </c>
       <c r="Y11" t="n">
         <v>0.05</v>
       </c>
       <c r="Z11" t="n">
-        <v>15.05</v>
+        <v>14.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.630000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.42</v>
+        <v>5.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.21</v>
+        <v>17.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
         <v>0.06</v>
@@ -5177,70 +5177,70 @@
         <v>1.78</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.140000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP11" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.78</v>
+        <v>4.89</v>
       </c>
       <c r="BR11" t="n">
-        <v>89.19</v>
+        <v>89.47</v>
       </c>
       <c r="BS11" t="n">
-        <v>70.27</v>
+        <v>71.05</v>
       </c>
       <c r="BT11" t="n">
-        <v>51.35</v>
+        <v>52.63</v>
       </c>
       <c r="BU11" t="n">
-        <v>32.43</v>
+        <v>31.58</v>
       </c>
       <c r="BV11" t="n">
-        <v>21.62</v>
+        <v>21.05</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BX11" t="n">
-        <v>54.05</v>
+        <v>52.63</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CC11" t="n">
         <v>2.7</v>
@@ -5252,7 +5252,7 @@
         <v>1.36</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CG11" t="n">
         <v>3.01</v>
@@ -5270,10 +5270,10 @@
         <v>1.72</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CN11" t="n">
         <v>1.63</v>
@@ -5282,16 +5282,16 @@
         <v>1.25</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CR11" t="n">
         <v>1.41</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CT11" t="n">
         <v>3.03</v>
@@ -5300,10 +5300,10 @@
         <v>1.45</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CX11" t="n">
         <v>1.75</v>
@@ -5324,49 +5324,49 @@
         <v>1.87</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="DE11" t="n">
         <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.08</v>
+        <v>101.87</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.19</v>
+        <v>5.34</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM11" t="n">
-        <v>70.34999999999999</v>
+        <v>71.03</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.57</v>
+        <v>11.34</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.06</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.68</v>
+        <v>6.55</v>
       </c>
       <c r="DS11" t="n">
         <v>0.08</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.67</v>
+        <v>50.92</v>
       </c>
       <c r="DW11" t="n">
         <v>0.03</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.68</v>
+        <v>14.58</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.43</v>
+        <v>9.42</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.24</v>
+        <v>5.16</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.4</v>
+        <v>17.89</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -5409,61 +5409,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F12" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="G12" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="H12" t="n">
-        <v>102.28</v>
+        <v>102.16</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="K12" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="L12" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="M12" t="n">
-        <v>62.83</v>
+        <v>63.95</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="O12" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="P12" t="n">
-        <v>11.44</v>
+        <v>11.47</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.72</v>
+        <v>11.95</v>
       </c>
       <c r="R12" t="n">
-        <v>9.220000000000001</v>
+        <v>9</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="U12" t="n">
         <v>0.11</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.72</v>
+        <v>15.68</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.11</v>
+        <v>10</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.61</v>
+        <v>5.68</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.06</v>
+        <v>17.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AF12" t="n">
         <v>0.16</v>
@@ -5580,70 +5580,70 @@
         <v>1.74</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.73</v>
+        <v>9.76</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.27</v>
+        <v>4.39</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.92</v>
+        <v>4.84</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS12" t="n">
-        <v>75.68000000000001</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>54.05</v>
+        <v>52.63</v>
       </c>
       <c r="BU12" t="n">
-        <v>32.43</v>
+        <v>31.58</v>
       </c>
       <c r="BV12" t="n">
-        <v>24.32</v>
+        <v>23.68</v>
       </c>
       <c r="BW12" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="BX12" t="n">
-        <v>67.56999999999999</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="CA12" t="n">
         <v>3.39</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="CC12" t="n">
         <v>3.49</v>
@@ -5652,13 +5652,13 @@
         <v>3.66</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF12" t="n">
         <v>2.7</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CH12" t="n">
         <v>1.43</v>
@@ -5694,7 +5694,7 @@
         <v>1.42</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CT12" t="n">
         <v>2.98</v>
@@ -5724,28 +5724,28 @@
         <v>1.28</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="DE12" t="n">
         <v>0.11</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="DH12" t="n">
-        <v>98.70999999999999</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="DK12" t="n">
         <v>4.13</v>
@@ -5754,22 +5754,22 @@
         <v>0.13</v>
       </c>
       <c r="DM12" t="n">
-        <v>63.24</v>
+        <v>63.79</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.78</v>
+        <v>10.82</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.84</v>
+        <v>11.95</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.779999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="DS12" t="n">
         <v>0.11</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>44.57</v>
+        <v>44.84</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.49</v>
+        <v>14.5</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.300000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.19</v>
+        <v>5.24</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.95</v>
+        <v>17.44</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="13">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" t="n">
         <v>19</v>
@@ -5824,82 +5824,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="G13" t="n">
-        <v>3.44</v>
+        <v>3.53</v>
       </c>
       <c r="H13" t="n">
-        <v>106.67</v>
+        <v>107.11</v>
       </c>
       <c r="I13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="J13" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="K13" t="n">
-        <v>5.78</v>
+        <v>5.74</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="M13" t="n">
-        <v>77.78</v>
+        <v>77.95</v>
       </c>
       <c r="N13" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="P13" t="n">
-        <v>10.06</v>
+        <v>10.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.83</v>
+        <v>11.95</v>
       </c>
       <c r="R13" t="n">
-        <v>6.11</v>
+        <v>5.89</v>
       </c>
       <c r="S13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="T13" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="U13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="V13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>58.67</v>
+        <v>58.26</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.78</v>
+        <v>15.47</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.44</v>
+        <v>11.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.33</v>
+        <v>4.42</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.89</v>
+        <v>19.74</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AF13" t="n">
         <v>0.16</v>
@@ -5983,61 +5983,61 @@
         <v>2.11</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.81</v>
+        <v>9.74</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.81</v>
+        <v>3.76</v>
       </c>
       <c r="BQ13" t="n">
         <v>5.32</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.59</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>72.97</v>
+        <v>71.05</v>
       </c>
       <c r="BT13" t="n">
-        <v>37.84</v>
+        <v>36.84</v>
       </c>
       <c r="BU13" t="n">
-        <v>24.32</v>
+        <v>23.68</v>
       </c>
       <c r="BV13" t="n">
-        <v>13.51</v>
+        <v>13.16</v>
       </c>
       <c r="BW13" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BX13" t="n">
-        <v>51.35</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BZ13" t="n">
         <v>1.96</v>
@@ -6046,7 +6046,7 @@
         <v>3.47</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CC13" t="n">
         <v>2.31</v>
@@ -6067,40 +6067,40 @@
         <v>1.41</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO13" t="n">
         <v>1.27</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CR13" t="n">
         <v>1.43</v>
       </c>
       <c r="CS13" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CU13" t="n">
         <v>1.42</v>
@@ -6112,67 +6112,67 @@
         <v>1.79</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CY13" t="n">
         <v>2.18</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DB13" t="n">
         <v>1.3</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="DE13" t="n">
         <v>0.08</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="DH13" t="n">
-        <v>106.62</v>
+        <v>106.84</v>
       </c>
       <c r="DI13" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.68</v>
+        <v>5.66</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM13" t="n">
-        <v>77.08</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.33</v>
+        <v>11.42</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.27</v>
+        <v>11.34</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.54</v>
+        <v>7.39</v>
       </c>
       <c r="DS13" t="n">
         <v>0.11</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.95</v>
+        <v>56.79</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.46</v>
+        <v>14.34</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.38</v>
+        <v>10.21</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.08</v>
+        <v>4.13</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.7</v>
+        <v>19.16</v>
       </c>
       <c r="EB13" t="n">
         <v>1.76</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
@@ -1508,7 +1508,7 @@
         <v>8.58</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.58</v>
+        <v>10.53</v>
       </c>
       <c r="AT2" t="n">
         <v>1.32</v>
@@ -1526,22 +1526,22 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>42.74</v>
+        <v>42.89</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.42</v>
+        <v>11.53</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.32</v>
+        <v>7.42</v>
       </c>
       <c r="BC2" t="n">
         <v>4.11</v>
       </c>
       <c r="BD2" t="n">
-        <v>18.11</v>
+        <v>18.79</v>
       </c>
       <c r="BE2" t="n">
         <v>1.43</v>
@@ -1739,7 +1739,7 @@
         <v>9.98</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.92</v>
+        <v>8.9</v>
       </c>
       <c r="DS2" t="n">
         <v>0.05</v>
@@ -1751,22 +1751,22 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>46.14</v>
+        <v>46.21</v>
       </c>
       <c r="DW2" t="n">
         <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.66</v>
+        <v>12.71</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.140000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="DZ2" t="n">
         <v>4.53</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.4</v>
+        <v>18.74</v>
       </c>
       <c r="EB2" t="n">
         <v>1.58</v>
@@ -1827,7 +1827,7 @@
         <v>9.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.11</v>
+        <v>11.89</v>
       </c>
       <c r="R3" t="n">
         <v>7.17</v>
@@ -1848,25 +1848,25 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>50.22</v>
+        <v>50.06</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.56</v>
+        <v>14.94</v>
       </c>
       <c r="AA3" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.56</v>
+        <v>4.61</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.28</v>
+        <v>18.56</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AE3" t="n">
         <v>1.67</v>
@@ -2139,7 +2139,7 @@
         <v>10.24</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.95</v>
+        <v>11.84</v>
       </c>
       <c r="DR3" t="n">
         <v>7.21</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>48.74</v>
+        <v>48.66</v>
       </c>
       <c r="DW3" t="n">
         <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.9</v>
+        <v>13.08</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.68</v>
+        <v>8.84</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.21</v>
+        <v>4.24</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.05</v>
+        <v>19.66</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="EC3" t="n">
         <v>1.61</v>
@@ -2311,7 +2311,7 @@
         <v>11.32</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.789999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="AS4" t="n">
         <v>9.32</v>
@@ -2332,25 +2332,25 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>48.11</v>
+        <v>47.89</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.11</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.79</v>
+        <v>11.16</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.63</v>
+        <v>7</v>
       </c>
       <c r="BC4" t="n">
         <v>4.16</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.63</v>
+        <v>17.21</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BF4" t="n">
         <v>1.79</v>
@@ -2542,7 +2542,7 @@
         <v>10.68</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.9</v>
+        <v>9.84</v>
       </c>
       <c r="DR4" t="n">
         <v>8.18</v>
@@ -2557,25 +2557,25 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>50.45</v>
+        <v>50.34</v>
       </c>
       <c r="DW4" t="n">
         <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.29</v>
+        <v>11.48</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.98</v>
+        <v>7.16</v>
       </c>
       <c r="DZ4" t="n">
         <v>4.32</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.76</v>
+        <v>17.05</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="EC4" t="n">
         <v>1.66</v>
@@ -2696,7 +2696,7 @@
         <v>1.58</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.37</v>
+        <v>5.42</v>
       </c>
       <c r="AM5" t="n">
         <v>0.32</v>
@@ -2714,7 +2714,7 @@
         <v>10.79</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.84</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AS5" t="n">
         <v>6.95</v>
@@ -2735,25 +2735,25 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52.53</v>
+        <v>52.26</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.79</v>
+        <v>14.21</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.050000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BC5" t="n">
         <v>4.74</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.26</v>
+        <v>18.53</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="BF5" t="n">
         <v>1.58</v>
@@ -2762,7 +2762,7 @@
         <v>2.68</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.869999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI5" t="n">
         <v>2.68</v>
@@ -2927,7 +2927,7 @@
         <v>1.71</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.56</v>
+        <v>5.58</v>
       </c>
       <c r="DL5" t="n">
         <v>0.34</v>
@@ -2945,7 +2945,7 @@
         <v>9.76</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.76</v>
+        <v>10.74</v>
       </c>
       <c r="DR5" t="n">
         <v>6.29</v>
@@ -2960,25 +2960,25 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.32</v>
+        <v>54.18</v>
       </c>
       <c r="DW5" t="n">
         <v>0.02</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.82</v>
+        <v>16.03</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.55</v>
+        <v>10.76</v>
       </c>
       <c r="DZ5" t="n">
         <v>5.26</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.6</v>
+        <v>19.24</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="EC5" t="n">
         <v>1.68</v>
@@ -3036,7 +3036,7 @@
         <v>10.11</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.63</v>
+        <v>11.53</v>
       </c>
       <c r="R6" t="n">
         <v>5.89</v>
@@ -3057,25 +3057,25 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>51</v>
+        <v>51.11</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.74</v>
+        <v>6.84</v>
       </c>
       <c r="AB6" t="n">
         <v>4.26</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.21</v>
+        <v>20.79</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
         <v>1.79</v>
@@ -3165,7 +3165,7 @@
         <v>2.05</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.529999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BI6" t="n">
         <v>2.05</v>
@@ -3348,7 +3348,7 @@
         <v>11.56</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.34</v>
+        <v>11.29</v>
       </c>
       <c r="DR6" t="n">
         <v>7.15</v>
@@ -3363,22 +3363,22 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.66</v>
+        <v>48.72</v>
       </c>
       <c r="DW6" t="n">
         <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.34</v>
+        <v>10.4</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="DZ6" t="n">
         <v>3.74</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.58</v>
+        <v>19.37</v>
       </c>
       <c r="EB6" t="n">
         <v>1.34</v>
@@ -3520,7 +3520,7 @@
         <v>10.68</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.16</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
         <v>8.42</v>
@@ -3541,25 +3541,25 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>46.84</v>
+        <v>47.16</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.05</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.369999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.79</v>
+        <v>6.16</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.58</v>
+        <v>3.53</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.53</v>
+        <v>17.32</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BF7" t="n">
         <v>2.37</v>
@@ -3751,7 +3751,7 @@
         <v>10.34</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.5</v>
+        <v>12.42</v>
       </c>
       <c r="DR7" t="n">
         <v>7.76</v>
@@ -3766,25 +3766,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.42</v>
+        <v>48.58</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.76</v>
+        <v>10.92</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.08</v>
+        <v>7.26</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.71</v>
+        <v>17.1</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="EC7" t="n">
         <v>2.02</v>
@@ -3923,10 +3923,10 @@
         <v>11.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.45</v>
+        <v>11.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.25</v>
+        <v>7.3</v>
       </c>
       <c r="AT8" t="n">
         <v>1.45</v>
@@ -3944,25 +3944,25 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>50.15</v>
+        <v>50.1</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.15</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.4</v>
+        <v>11.55</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.45</v>
+        <v>18.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="BF8" t="n">
         <v>1.8</v>
@@ -4154,10 +4154,10 @@
         <v>11.89</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.81</v>
+        <v>11.79</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.21</v>
+        <v>7.24</v>
       </c>
       <c r="DS8" t="n">
         <v>0.08</v>
@@ -4169,25 +4169,25 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.66</v>
+        <v>50.63</v>
       </c>
       <c r="DW8" t="n">
         <v>0.21</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.31</v>
+        <v>12.39</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.210000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.1</v>
+        <v>4.13</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.71</v>
+        <v>20.21</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="EC8" t="n">
         <v>1.87</v>
@@ -4245,10 +4245,10 @@
         <v>10.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.4</v>
+        <v>10.35</v>
       </c>
       <c r="R9" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="S9" t="n">
         <v>1.05</v>
@@ -4266,25 +4266,25 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>52.3</v>
+        <v>52.55</v>
       </c>
       <c r="Y9" t="n">
         <v>0.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.8</v>
+        <v>13.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.8</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AB9" t="n">
         <v>5</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.05</v>
+        <v>18.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AE9" t="n">
         <v>1.85</v>
@@ -4374,7 +4374,7 @@
         <v>2.53</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.630000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="BI9" t="n">
         <v>2.53</v>
@@ -4557,10 +4557,10 @@
         <v>11.9</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.55</v>
+        <v>10.53</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.19</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0.18</v>
@@ -4572,25 +4572,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.92</v>
+        <v>50.05</v>
       </c>
       <c r="DW9" t="n">
         <v>0.03</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.68</v>
+        <v>11.81</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.37</v>
+        <v>7.5</v>
       </c>
       <c r="DZ9" t="n">
         <v>4.32</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.26</v>
+        <v>17.61</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="EC9" t="n">
         <v>2.24</v>
@@ -4711,7 +4711,7 @@
         <v>1.63</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.63</v>
+        <v>3.68</v>
       </c>
       <c r="AM10" t="n">
         <v>0.11</v>
@@ -4729,7 +4729,7 @@
         <v>12.37</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.74</v>
+        <v>11.68</v>
       </c>
       <c r="AS10" t="n">
         <v>8.630000000000001</v>
@@ -4750,22 +4750,22 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>47.42</v>
+        <v>47.32</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.11</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.529999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="BC10" t="n">
         <v>3.47</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.47</v>
+        <v>20</v>
       </c>
       <c r="BE10" t="n">
         <v>1.29</v>
@@ -4777,7 +4777,7 @@
         <v>2.29</v>
       </c>
       <c r="BH10" t="n">
-        <v>8</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="BI10" t="n">
         <v>2.29</v>
@@ -4942,7 +4942,7 @@
         <v>1.6</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.34</v>
+        <v>4.36</v>
       </c>
       <c r="DL10" t="n">
         <v>0.18</v>
@@ -4960,7 +4960,7 @@
         <v>11.76</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.45</v>
+        <v>12.42</v>
       </c>
       <c r="DR10" t="n">
         <v>7.58</v>
@@ -4975,22 +4975,22 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.15</v>
+        <v>50.1</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.92</v>
+        <v>11.9</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.79</v>
+        <v>7.76</v>
       </c>
       <c r="DZ10" t="n">
         <v>4.13</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.29</v>
+        <v>20.05</v>
       </c>
       <c r="EB10" t="n">
         <v>1.5</v>
@@ -5051,10 +5051,10 @@
         <v>10.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.1</v>
+        <v>10.15</v>
       </c>
       <c r="R11" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="S11" t="n">
         <v>0.95</v>
@@ -5072,25 +5072,25 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>52.65</v>
+        <v>52.85</v>
       </c>
       <c r="Y11" t="n">
         <v>0.05</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.85</v>
+        <v>15.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="AB11" t="n">
         <v>5.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.25</v>
+        <v>17.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AE11" t="n">
         <v>1.05</v>
@@ -5363,10 +5363,10 @@
         <v>11.34</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.050000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.55</v>
+        <v>6.61</v>
       </c>
       <c r="DS11" t="n">
         <v>0.08</v>
@@ -5378,25 +5378,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.92</v>
+        <v>51.03</v>
       </c>
       <c r="DW11" t="n">
         <v>0.03</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.58</v>
+        <v>14.84</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.42</v>
+        <v>9.68</v>
       </c>
       <c r="DZ11" t="n">
         <v>5.16</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.89</v>
+        <v>18.24</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="EC11" t="n">
         <v>1.4</v>
@@ -5454,7 +5454,7 @@
         <v>11.47</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.95</v>
+        <v>11.84</v>
       </c>
       <c r="R12" t="n">
         <v>9</v>
@@ -5475,25 +5475,25 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>46</v>
+        <v>45.68</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.68</v>
+        <v>15.95</v>
       </c>
       <c r="AA12" t="n">
-        <v>10</v>
+        <v>10.32</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.68</v>
+        <v>5.63</v>
       </c>
       <c r="AC12" t="n">
-        <v>17.05</v>
+        <v>18.37</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AE12" t="n">
         <v>1.53</v>
@@ -5766,7 +5766,7 @@
         <v>10.82</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.95</v>
+        <v>11.9</v>
       </c>
       <c r="DR12" t="n">
         <v>8.68</v>
@@ -5781,22 +5781,22 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>44.84</v>
+        <v>44.68</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.5</v>
+        <v>14.64</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.26</v>
+        <v>9.42</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.24</v>
+        <v>5.21</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.44</v>
+        <v>18.1</v>
       </c>
       <c r="EB12" t="n">
         <v>1.74</v>
@@ -5857,7 +5857,7 @@
         <v>10.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.95</v>
+        <v>11.84</v>
       </c>
       <c r="R13" t="n">
         <v>5.89</v>
@@ -5878,25 +5878,25 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>58.26</v>
+        <v>58.32</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.47</v>
+        <v>15.63</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.05</v>
+        <v>11.21</v>
       </c>
       <c r="AB13" t="n">
         <v>4.42</v>
       </c>
       <c r="AC13" t="n">
-        <v>19.74</v>
+        <v>21.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AE13" t="n">
         <v>1.89</v>
@@ -6169,7 +6169,7 @@
         <v>11.42</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.34</v>
+        <v>11.29</v>
       </c>
       <c r="DR13" t="n">
         <v>7.39</v>
@@ -6184,22 +6184,22 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.79</v>
+        <v>56.82</v>
       </c>
       <c r="DW13" t="n">
         <v>0.05</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.34</v>
+        <v>14.42</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.21</v>
+        <v>10.29</v>
       </c>
       <c r="DZ13" t="n">
         <v>4.13</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.16</v>
+        <v>20.26</v>
       </c>
       <c r="EB13" t="n">
         <v>1.76</v>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
@@ -1394,7 +1394,7 @@
         <v>1.21</v>
       </c>
       <c r="G2" t="n">
-        <v>2.37</v>
+        <v>2.84</v>
       </c>
       <c r="H2" t="n">
         <v>105.47</v>
@@ -1409,7 +1409,7 @@
         <v>5.32</v>
       </c>
       <c r="L2" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="M2" t="n">
         <v>69.42</v>
@@ -1418,7 +1418,7 @@
         <v>0.37</v>
       </c>
       <c r="O2" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="P2" t="n">
         <v>10.26</v>
@@ -1505,7 +1505,7 @@
         <v>12.11</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.58</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AS2" t="n">
         <v>10.53</v>
@@ -1532,10 +1532,10 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.53</v>
+        <v>11.58</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.42</v>
+        <v>7.47</v>
       </c>
       <c r="BC2" t="n">
         <v>4.11</v>
@@ -1544,7 +1544,7 @@
         <v>18.79</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="BF2" t="n">
         <v>2.53</v>
@@ -1577,10 +1577,10 @@
         <v>1.11</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.03</v>
+        <v>4.08</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.03</v>
+        <v>5.32</v>
       </c>
       <c r="BR2" t="n">
         <v>94.73999999999999</v>
@@ -1706,7 +1706,7 @@
         <v>1.44</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="DH2" t="n">
         <v>99.59999999999999</v>
@@ -1721,7 +1721,7 @@
         <v>4.24</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="DM2" t="n">
         <v>63.5</v>
@@ -1730,13 +1730,13 @@
         <v>0.6</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="DP2" t="n">
         <v>11.18</v>
       </c>
       <c r="DQ2" t="n">
-        <v>9.98</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DR2" t="n">
         <v>8.9</v>
@@ -1757,10 +1757,10 @@
         <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.71</v>
+        <v>12.74</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.18</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DZ2" t="n">
         <v>4.53</v>
@@ -1794,7 +1794,7 @@
         <v>0.06</v>
       </c>
       <c r="F3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>2.89</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="K3" t="n">
         <v>5.33</v>
@@ -1869,7 +1869,7 @@
         <v>1.76</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AF3" t="n">
         <v>0.1</v>
@@ -1878,7 +1878,7 @@
         <v>1.1</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AI3" t="n">
         <v>97.55</v>
@@ -1893,7 +1893,7 @@
         <v>3.75</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="AN3" t="n">
         <v>55.9</v>
@@ -1902,7 +1902,7 @@
         <v>0.55</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AQ3" t="n">
         <v>10.75</v>
@@ -1929,25 +1929,25 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>47.4</v>
+        <v>47.45</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.4</v>
+        <v>11.45</v>
       </c>
       <c r="BB3" t="n">
         <v>7.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BD3" t="n">
         <v>20.65</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BF3" t="n">
         <v>1.55</v>
@@ -1980,10 +1980,10 @@
         <v>1.24</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.32</v>
+        <v>4.53</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="BR3" t="n">
         <v>97.37</v>
@@ -2106,10 +2106,10 @@
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DH3" t="n">
         <v>103.76</v>
@@ -2118,13 +2118,13 @@
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="DK3" t="n">
         <v>4.5</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="DM3" t="n">
         <v>61.63</v>
@@ -2133,7 +2133,7 @@
         <v>0.58</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="DP3" t="n">
         <v>10.24</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>48.66</v>
+        <v>48.69</v>
       </c>
       <c r="DW3" t="n">
         <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.08</v>
+        <v>13.1</v>
       </c>
       <c r="DY3" t="n">
         <v>8.84</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="EA3" t="n">
         <v>19.66</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="4">
@@ -2197,10 +2197,10 @@
         <v>0.05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="G4" t="n">
-        <v>2.05</v>
+        <v>2.53</v>
       </c>
       <c r="H4" t="n">
         <v>119.26</v>
@@ -2209,13 +2209,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="K4" t="n">
         <v>4.21</v>
       </c>
       <c r="L4" t="n">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="M4" t="n">
         <v>69.79000000000001</v>
@@ -2224,7 +2224,7 @@
         <v>0.47</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.68</v>
       </c>
       <c r="P4" t="n">
         <v>10.05</v>
@@ -2272,13 +2272,13 @@
         <v>1.57</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AF4" t="n">
         <v>0.32</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AH4" t="n">
         <v>1.21</v>
@@ -2290,7 +2290,7 @@
         <v>0.16</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AL4" t="n">
         <v>3.53</v>
@@ -2323,10 +2323,10 @@
         <v>1.68</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
@@ -2353,7 +2353,7 @@
         <v>1.43</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="BG4" t="n">
         <v>2.74</v>
@@ -2383,10 +2383,10 @@
         <v>0.95</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.29</v>
+        <v>3.61</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.11</v>
+        <v>4.47</v>
       </c>
       <c r="BR4" t="n">
         <v>92.11</v>
@@ -2509,10 +2509,10 @@
         <v>0.18</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="DH4" t="n">
         <v>107.29</v>
@@ -2521,13 +2521,13 @@
         <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="DK4" t="n">
         <v>3.87</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DM4" t="n">
         <v>65.06</v>
@@ -2536,7 +2536,7 @@
         <v>0.68</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="DP4" t="n">
         <v>10.68</v>
@@ -2548,10 +2548,10 @@
         <v>8.18</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
         <v>1.5</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="5">
@@ -2603,7 +2603,7 @@
         <v>1.26</v>
       </c>
       <c r="G5" t="n">
-        <v>3.47</v>
+        <v>3.32</v>
       </c>
       <c r="H5" t="n">
         <v>105.37</v>
@@ -2618,7 +2618,7 @@
         <v>5.74</v>
       </c>
       <c r="L5" t="n">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="M5" t="n">
         <v>68.89</v>
@@ -2627,7 +2627,7 @@
         <v>0.58</v>
       </c>
       <c r="O5" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="P5" t="n">
         <v>8.74</v>
@@ -2684,7 +2684,7 @@
         <v>1.05</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.79</v>
+        <v>3.21</v>
       </c>
       <c r="AI5" t="n">
         <v>98.26000000000001</v>
@@ -2699,7 +2699,7 @@
         <v>5.42</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="AN5" t="n">
         <v>68.20999999999999</v>
@@ -2708,7 +2708,7 @@
         <v>0.53</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AQ5" t="n">
         <v>10.79</v>
@@ -2786,10 +2786,10 @@
         <v>1.05</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.53</v>
+        <v>3.74</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.61</v>
+        <v>4.82</v>
       </c>
       <c r="BR5" t="n">
         <v>86.84</v>
@@ -2915,7 +2915,7 @@
         <v>1.16</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.13</v>
+        <v>3.26</v>
       </c>
       <c r="DH5" t="n">
         <v>101.82</v>
@@ -2930,7 +2930,7 @@
         <v>5.58</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="DM5" t="n">
         <v>68.55</v>
@@ -2939,7 +2939,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="DP5" t="n">
         <v>9.76</v>
@@ -3006,7 +3006,7 @@
         <v>1.11</v>
       </c>
       <c r="G6" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="H6" t="n">
         <v>98</v>
@@ -3021,7 +3021,7 @@
         <v>4.79</v>
       </c>
       <c r="L6" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="M6" t="n">
         <v>61.42</v>
@@ -3030,7 +3030,7 @@
         <v>0.68</v>
       </c>
       <c r="O6" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="P6" t="n">
         <v>10.11</v>
@@ -3084,10 +3084,10 @@
         <v>0.11</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="AI6" t="n">
         <v>94.16</v>
@@ -3096,13 +3096,13 @@
         <v>0.05</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AL6" t="n">
         <v>3.84</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="AN6" t="n">
         <v>53.42</v>
@@ -3111,7 +3111,7 @@
         <v>0.89</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="AQ6" t="n">
         <v>13</v>
@@ -3144,13 +3144,13 @@
         <v>0.16</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.68</v>
+        <v>9.74</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.47</v>
+        <v>6.58</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="BD6" t="n">
         <v>17.95</v>
@@ -3159,7 +3159,7 @@
         <v>1.23</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="BG6" t="n">
         <v>2.05</v>
@@ -3189,10 +3189,10 @@
         <v>0.76</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.29</v>
+        <v>3.55</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.29</v>
+        <v>4.58</v>
       </c>
       <c r="BR6" t="n">
         <v>84.20999999999999</v>
@@ -3315,10 +3315,10 @@
         <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="DH6" t="n">
         <v>96.08</v>
@@ -3327,13 +3327,13 @@
         <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="DK6" t="n">
         <v>4.32</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="DM6" t="n">
         <v>57.42</v>
@@ -3342,7 +3342,7 @@
         <v>0.78</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="DP6" t="n">
         <v>11.56</v>
@@ -3369,13 +3369,13 @@
         <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.4</v>
+        <v>10.42</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.65</v>
+        <v>6.71</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="EA6" t="n">
         <v>19.37</v>
@@ -3384,7 +3384,7 @@
         <v>1.34</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="7">
@@ -3409,7 +3409,7 @@
         <v>1.11</v>
       </c>
       <c r="G7" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="H7" t="n">
         <v>112.63</v>
@@ -3424,7 +3424,7 @@
         <v>3.63</v>
       </c>
       <c r="L7" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="M7" t="n">
         <v>77.37</v>
@@ -3433,7 +3433,7 @@
         <v>0.68</v>
       </c>
       <c r="O7" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="P7" t="n">
         <v>10</v>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>47.16</v>
+        <v>47.21</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.05</v>
@@ -3592,10 +3592,10 @@
         <v>0.89</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.5</v>
+        <v>4.61</v>
       </c>
       <c r="BR7" t="n">
         <v>92.11</v>
@@ -3721,7 +3721,7 @@
         <v>1.22</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="DH7" t="n">
         <v>104.55</v>
@@ -3736,7 +3736,7 @@
         <v>4</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="DM7" t="n">
         <v>67.58</v>
@@ -3745,7 +3745,7 @@
         <v>0.9</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DP7" t="n">
         <v>10.34</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.58</v>
+        <v>48.6</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
@@ -3812,7 +3812,7 @@
         <v>1.44</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="H8" t="n">
         <v>93.94</v>
@@ -3827,7 +3827,7 @@
         <v>4.06</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="M8" t="n">
         <v>61.17</v>
@@ -3836,7 +3836,7 @@
         <v>0.78</v>
       </c>
       <c r="O8" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="P8" t="n">
         <v>12</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>50.1</v>
+        <v>50.05</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.15</v>
@@ -3995,10 +3995,10 @@
         <v>0.76</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.63</v>
+        <v>3.84</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.92</v>
+        <v>4.97</v>
       </c>
       <c r="BR8" t="n">
         <v>92.11</v>
@@ -4124,7 +4124,7 @@
         <v>1.29</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="DH8" t="n">
         <v>97.97</v>
@@ -4139,7 +4139,7 @@
         <v>3.9</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="DM8" t="n">
         <v>60.03</v>
@@ -4148,7 +4148,7 @@
         <v>0.79</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="DP8" t="n">
         <v>11.89</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.63</v>
+        <v>50.6</v>
       </c>
       <c r="DW8" t="n">
         <v>0.21</v>
@@ -4215,7 +4215,7 @@
         <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
         <v>117.6</v>
@@ -4230,7 +4230,7 @@
         <v>4.8</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="M9" t="n">
         <v>83.2</v>
@@ -4239,7 +4239,7 @@
         <v>0.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
         <v>10.65</v>
@@ -4353,10 +4353,10 @@
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.44</v>
+        <v>10.39</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.89</v>
+        <v>6.83</v>
       </c>
       <c r="BC9" t="n">
         <v>3.56</v>
@@ -4365,7 +4365,7 @@
         <v>16.39</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BF9" t="n">
         <v>2.67</v>
@@ -4398,10 +4398,10 @@
         <v>1.13</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.21</v>
+        <v>3.42</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.89</v>
+        <v>5.11</v>
       </c>
       <c r="BR9" t="n">
         <v>92.11</v>
@@ -4527,7 +4527,7 @@
         <v>1.55</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="DH9" t="n">
         <v>106.81</v>
@@ -4542,7 +4542,7 @@
         <v>4.37</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="DM9" t="n">
         <v>71.03</v>
@@ -4551,7 +4551,7 @@
         <v>0.71</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="DP9" t="n">
         <v>11.9</v>
@@ -4578,10 +4578,10 @@
         <v>0.03</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.81</v>
+        <v>11.79</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.5</v>
+        <v>7.47</v>
       </c>
       <c r="DZ9" t="n">
         <v>4.32</v>
@@ -4590,7 +4590,7 @@
         <v>17.61</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="EC9" t="n">
         <v>2.24</v>
@@ -4696,10 +4696,10 @@
         <v>0.11</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AI10" t="n">
         <v>107.21</v>
@@ -4708,13 +4708,13 @@
         <v>0.05</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AL10" t="n">
         <v>3.68</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="AN10" t="n">
         <v>60.21</v>
@@ -4723,7 +4723,7 @@
         <v>0.74</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AQ10" t="n">
         <v>12.37</v>
@@ -4756,13 +4756,13 @@
         <v>0.11</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.470000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BB10" t="n">
         <v>6</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.47</v>
+        <v>3.53</v>
       </c>
       <c r="BD10" t="n">
         <v>20</v>
@@ -4771,7 +4771,7 @@
         <v>1.29</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="BG10" t="n">
         <v>2.29</v>
@@ -4801,10 +4801,10 @@
         <v>1.11</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.16</v>
+        <v>3.37</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.18</v>
+        <v>4.34</v>
       </c>
       <c r="BR10" t="n">
         <v>92.11</v>
@@ -4927,10 +4927,10 @@
         <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="DH10" t="n">
         <v>104.68</v>
@@ -4939,13 +4939,13 @@
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="DK10" t="n">
         <v>4.36</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="DM10" t="n">
         <v>63.32</v>
@@ -4954,7 +4954,7 @@
         <v>0.66</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="DP10" t="n">
         <v>11.76</v>
@@ -4981,13 +4981,13 @@
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.9</v>
+        <v>11.92</v>
       </c>
       <c r="DY10" t="n">
         <v>7.76</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.13</v>
+        <v>4.16</v>
       </c>
       <c r="EA10" t="n">
         <v>20.05</v>
@@ -4996,7 +4996,7 @@
         <v>1.5</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="11">
@@ -5018,10 +5018,10 @@
         <v>0.05</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="G11" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="H11" t="n">
         <v>106.5</v>
@@ -5030,13 +5030,13 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="K11" t="n">
         <v>5.8</v>
       </c>
       <c r="L11" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="M11" t="n">
         <v>71.7</v>
@@ -5045,7 +5045,7 @@
         <v>0.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
         <v>10.75</v>
@@ -5093,7 +5093,7 @@
         <v>1.85</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF11" t="n">
         <v>0.06</v>
@@ -5102,7 +5102,7 @@
         <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AI11" t="n">
         <v>96.72</v>
@@ -5117,7 +5117,7 @@
         <v>4.83</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="AN11" t="n">
         <v>70.28</v>
@@ -5126,7 +5126,7 @@
         <v>0.44</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ11" t="n">
         <v>12</v>
@@ -5204,7 +5204,7 @@
         <v>1.13</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.03</v>
+        <v>4.05</v>
       </c>
       <c r="BQ11" t="n">
         <v>4.89</v>
@@ -5330,10 +5330,10 @@
         <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="DH11" t="n">
         <v>101.87</v>
@@ -5342,13 +5342,13 @@
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="DK11" t="n">
         <v>5.34</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="DM11" t="n">
         <v>71.03</v>
@@ -5357,7 +5357,7 @@
         <v>0.37</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DP11" t="n">
         <v>11.34</v>
@@ -5399,7 +5399,7 @@
         <v>1.81</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="12">
@@ -5481,19 +5481,19 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.95</v>
+        <v>16</v>
       </c>
       <c r="AA12" t="n">
         <v>10.32</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.63</v>
+        <v>5.68</v>
       </c>
       <c r="AC12" t="n">
         <v>18.37</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AE12" t="n">
         <v>1.53</v>
@@ -5502,10 +5502,10 @@
         <v>0.16</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="AI12" t="n">
         <v>95.31999999999999</v>
@@ -5514,13 +5514,13 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AL12" t="n">
         <v>4.63</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="AN12" t="n">
         <v>63.63</v>
@@ -5529,7 +5529,7 @@
         <v>0.37</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AQ12" t="n">
         <v>10.16</v>
@@ -5577,7 +5577,7 @@
         <v>1.63</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="BG12" t="n">
         <v>2.87</v>
@@ -5607,10 +5607,10 @@
         <v>1.18</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.39</v>
+        <v>4.47</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.84</v>
+        <v>4.92</v>
       </c>
       <c r="BR12" t="n">
         <v>92.11</v>
@@ -5733,10 +5733,10 @@
         <v>0.11</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="DH12" t="n">
         <v>98.73999999999999</v>
@@ -5745,13 +5745,13 @@
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DK12" t="n">
         <v>4.13</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DM12" t="n">
         <v>63.79</v>
@@ -5760,7 +5760,7 @@
         <v>0.42</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="DP12" t="n">
         <v>10.82</v>
@@ -5787,22 +5787,22 @@
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.64</v>
+        <v>14.66</v>
       </c>
       <c r="DY12" t="n">
         <v>9.42</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.21</v>
+        <v>5.24</v>
       </c>
       <c r="EA12" t="n">
         <v>18.1</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="13">
@@ -5878,16 +5878,16 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>58.32</v>
+        <v>58.26</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.63</v>
+        <v>15.68</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.21</v>
+        <v>11.26</v>
       </c>
       <c r="AB13" t="n">
         <v>4.42</v>
@@ -5908,7 +5908,7 @@
         <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.53</v>
+        <v>2.89</v>
       </c>
       <c r="AI13" t="n">
         <v>106.58</v>
@@ -5923,7 +5923,7 @@
         <v>5.58</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="AN13" t="n">
         <v>76.42</v>
@@ -5932,7 +5932,7 @@
         <v>0.89</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.26</v>
+        <v>2.68</v>
       </c>
       <c r="AQ13" t="n">
         <v>12.53</v>
@@ -6010,10 +6010,10 @@
         <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.32</v>
+        <v>5.71</v>
       </c>
       <c r="BR13" t="n">
         <v>94.73999999999999</v>
@@ -6139,7 +6139,7 @@
         <v>1.24</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.03</v>
+        <v>3.21</v>
       </c>
       <c r="DH13" t="n">
         <v>106.84</v>
@@ -6154,7 +6154,7 @@
         <v>5.66</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="DM13" t="n">
         <v>77.18000000000001</v>
@@ -6163,7 +6163,7 @@
         <v>0.82</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="DP13" t="n">
         <v>11.42</v>
@@ -6184,16 +6184,16 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.82</v>
+        <v>56.79</v>
       </c>
       <c r="DW13" t="n">
         <v>0.05</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.42</v>
+        <v>14.45</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.29</v>
+        <v>10.32</v>
       </c>
       <c r="DZ13" t="n">
         <v>4.13</v>

--- a/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
+++ b/data/teams/leagues/Averages_South_Korea_K_League_1_2025.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,667 +694,667 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
